--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_attendance.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_attendance.xlsx
@@ -53003,10 +53003,10 @@
         <v>21</v>
       </c>
       <c r="J350" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K350" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L350" s="6" t="n">
         <v>27</v>
@@ -53018,7 +53018,7 @@
         <v>0</v>
       </c>
       <c r="O350" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P350" s="7" t="n">
         <v>27</v>
@@ -53029,10 +53029,8 @@
       <c r="R350" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S350" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S350" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T350" s="7" t="inlineStr">
         <is>
@@ -53205,10 +53203,10 @@
         <v>21</v>
       </c>
       <c r="J351" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K351" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L351" s="6" t="n">
         <v>27</v>
@@ -53220,7 +53218,7 @@
         <v>0</v>
       </c>
       <c r="O351" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P351" s="7" t="n">
         <v>27</v>
@@ -53231,10 +53229,8 @@
       <c r="R351" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S351" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S351" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T351" s="7" t="inlineStr">
         <is>
@@ -53407,10 +53403,10 @@
         <v>21</v>
       </c>
       <c r="J352" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K352" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L352" s="6" t="n">
         <v>27</v>
@@ -53422,7 +53418,7 @@
         <v>0</v>
       </c>
       <c r="O352" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P352" s="7" t="n">
         <v>27</v>
@@ -53433,10 +53429,8 @@
       <c r="R352" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S352" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S352" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T352" s="7" t="inlineStr">
         <is>
@@ -53609,10 +53603,10 @@
         <v>21</v>
       </c>
       <c r="J353" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K353" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L353" s="6" t="n">
         <v>27</v>
@@ -53624,7 +53618,7 @@
         <v>0</v>
       </c>
       <c r="O353" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P353" s="7" t="n">
         <v>27</v>
@@ -53635,10 +53629,8 @@
       <c r="R353" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S353" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S353" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T353" s="7" t="inlineStr">
         <is>
@@ -53811,10 +53803,10 @@
         <v>21</v>
       </c>
       <c r="J354" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K354" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L354" s="6" t="n">
         <v>27</v>
@@ -53826,7 +53818,7 @@
         <v>0</v>
       </c>
       <c r="O354" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P354" s="7" t="n">
         <v>27</v>
@@ -53837,10 +53829,8 @@
       <c r="R354" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S354" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S354" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T354" s="7" t="inlineStr">
         <is>
@@ -54013,10 +54003,10 @@
         <v>21</v>
       </c>
       <c r="J355" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K355" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L355" s="6" t="n">
         <v>27</v>
@@ -54028,7 +54018,7 @@
         <v>0</v>
       </c>
       <c r="O355" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P355" s="7" t="n">
         <v>27</v>
@@ -54039,10 +54029,8 @@
       <c r="R355" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S355" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S355" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T355" s="7" t="inlineStr">
         <is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_attendance.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_attendance.xlsx
@@ -78574,7 +78574,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -78647,7 +78647,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -78684,7 +78684,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -78716,7 +78716,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -78748,7 +78748,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -78780,7 +78780,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -78817,7 +78817,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -78854,7 +78854,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -78886,7 +78886,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -78918,7 +78918,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -78950,7 +78950,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -78987,7 +78987,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79019,7 +79019,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79051,7 +79051,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79083,7 +79083,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79115,7 +79115,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79147,7 +79147,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79179,7 +79179,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79216,7 +79216,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79248,7 +79248,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79285,7 +79285,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79322,7 +79322,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79359,7 +79359,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79391,7 +79391,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79428,7 +79428,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79460,7 +79460,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79492,7 +79492,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79529,7 +79529,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79566,7 +79566,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79598,7 +79598,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79635,7 +79635,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79672,7 +79672,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79709,7 +79709,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79741,7 +79741,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79778,7 +79778,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79815,7 +79815,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79852,7 +79852,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79884,7 +79884,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79916,7 +79916,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79948,7 +79948,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -79985,7 +79985,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80017,7 +80017,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80049,7 +80049,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80086,7 +80086,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80123,7 +80123,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80155,7 +80155,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80192,7 +80192,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80229,7 +80229,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80261,7 +80261,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80293,7 +80293,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80325,7 +80325,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80362,7 +80362,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80399,7 +80399,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80436,7 +80436,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80473,7 +80473,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80505,7 +80505,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80542,7 +80542,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80579,7 +80579,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80616,7 +80616,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80648,7 +80648,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80685,7 +80685,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80722,7 +80722,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80759,7 +80759,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80796,7 +80796,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80828,7 +80828,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80865,7 +80865,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80897,7 +80897,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80934,7 +80934,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -80966,7 +80966,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81003,7 +81003,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81040,7 +81040,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81077,7 +81077,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81114,7 +81114,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81151,7 +81151,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81183,7 +81183,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81220,7 +81220,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81257,7 +81257,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81294,7 +81294,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81331,7 +81331,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81368,7 +81368,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81405,7 +81405,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81442,7 +81442,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81479,7 +81479,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81516,7 +81516,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81553,7 +81553,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81590,7 +81590,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81627,7 +81627,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81659,7 +81659,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81696,7 +81696,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81733,7 +81733,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81770,7 +81770,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81807,7 +81807,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81844,7 +81844,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81876,7 +81876,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81908,7 +81908,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81945,7 +81945,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -81982,7 +81982,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82019,7 +82019,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82056,7 +82056,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82088,7 +82088,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82125,7 +82125,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82162,7 +82162,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82199,7 +82199,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82231,7 +82231,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82268,7 +82268,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82300,7 +82300,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82332,7 +82332,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82364,7 +82364,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82401,7 +82401,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82438,7 +82438,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82470,7 +82470,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82507,7 +82507,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82544,7 +82544,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82581,7 +82581,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82618,7 +82618,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82650,7 +82650,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82687,7 +82687,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82719,7 +82719,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82756,7 +82756,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82788,7 +82788,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82820,7 +82820,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82857,7 +82857,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82894,7 +82894,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82931,7 +82931,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -82968,7 +82968,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83005,7 +83005,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83037,7 +83037,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83069,7 +83069,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83106,7 +83106,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83143,7 +83143,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83180,7 +83180,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83212,7 +83212,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83249,7 +83249,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83286,7 +83286,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83323,7 +83323,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83360,7 +83360,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83397,7 +83397,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83434,7 +83434,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83471,7 +83471,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83503,7 +83503,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83535,7 +83535,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83567,7 +83567,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83604,7 +83604,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83641,7 +83641,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83678,7 +83678,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83710,7 +83710,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83747,7 +83747,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83784,7 +83784,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83821,7 +83821,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83858,7 +83858,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83895,7 +83895,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83927,7 +83927,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83959,7 +83959,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -83996,7 +83996,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84033,7 +84033,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84070,7 +84070,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84107,7 +84107,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84144,7 +84144,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84181,7 +84181,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84218,7 +84218,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84250,7 +84250,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84287,7 +84287,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84324,7 +84324,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84356,7 +84356,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84388,7 +84388,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84425,7 +84425,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84457,7 +84457,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84494,7 +84494,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84531,7 +84531,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84568,7 +84568,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84600,7 +84600,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84637,7 +84637,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84674,7 +84674,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84706,7 +84706,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84743,7 +84743,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84775,7 +84775,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84807,7 +84807,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84839,7 +84839,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84871,7 +84871,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84903,7 +84903,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84935,7 +84935,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84967,7 +84967,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -84999,7 +84999,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85031,7 +85031,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85063,7 +85063,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85095,7 +85095,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85127,7 +85127,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85159,7 +85159,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85191,7 +85191,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85223,7 +85223,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85255,7 +85255,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85287,7 +85287,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85319,7 +85319,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85351,7 +85351,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85383,7 +85383,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85415,7 +85415,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85447,7 +85447,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85479,7 +85479,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85511,7 +85511,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85543,7 +85543,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85575,7 +85575,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85607,7 +85607,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85639,7 +85639,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85671,7 +85671,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85703,7 +85703,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85735,7 +85735,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85767,7 +85767,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85799,7 +85799,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85831,7 +85831,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85863,7 +85863,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85895,7 +85895,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85927,7 +85927,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85959,7 +85959,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -85991,7 +85991,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86023,7 +86023,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86055,7 +86055,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86087,7 +86087,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86119,7 +86119,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86151,7 +86151,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86183,7 +86183,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86215,7 +86215,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86247,7 +86247,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86279,7 +86279,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86311,7 +86311,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86343,7 +86343,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86375,7 +86375,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86407,7 +86407,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86439,7 +86439,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86471,7 +86471,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86503,7 +86503,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86535,7 +86535,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86567,7 +86567,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86599,7 +86599,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86631,7 +86631,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86663,7 +86663,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86695,7 +86695,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86727,7 +86727,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86759,7 +86759,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86791,7 +86791,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86823,7 +86823,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86855,7 +86855,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86887,7 +86887,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86919,7 +86919,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86951,7 +86951,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -86983,7 +86983,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87015,7 +87015,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87047,7 +87047,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87079,7 +87079,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87111,7 +87111,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87143,7 +87143,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87175,7 +87175,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87207,7 +87207,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87239,7 +87239,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87271,7 +87271,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87303,7 +87303,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87335,7 +87335,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87367,7 +87367,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87399,7 +87399,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87431,7 +87431,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87463,7 +87463,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87495,7 +87495,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87527,7 +87527,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87559,7 +87559,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87591,7 +87591,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87623,7 +87623,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87655,7 +87655,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87687,7 +87687,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87719,7 +87719,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87751,7 +87751,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87783,7 +87783,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87815,7 +87815,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87847,7 +87847,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87879,7 +87879,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87911,7 +87911,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87943,7 +87943,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -87975,7 +87975,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88007,7 +88007,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88039,7 +88039,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88071,7 +88071,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88103,7 +88103,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88135,7 +88135,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88167,7 +88167,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88199,7 +88199,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88231,7 +88231,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88263,7 +88263,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88295,7 +88295,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88327,7 +88327,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88359,7 +88359,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88391,7 +88391,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88423,7 +88423,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88455,7 +88455,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88487,7 +88487,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88519,7 +88519,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88551,7 +88551,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88583,7 +88583,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88615,7 +88615,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88647,7 +88647,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88679,7 +88679,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88711,7 +88711,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88743,7 +88743,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88775,7 +88775,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88807,7 +88807,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88839,7 +88839,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88871,7 +88871,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88903,7 +88903,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88935,7 +88935,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88967,7 +88967,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -88999,7 +88999,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89031,7 +89031,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89063,7 +89063,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89095,7 +89095,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89127,7 +89127,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89159,7 +89159,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89191,7 +89191,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89223,7 +89223,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89255,7 +89255,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89287,7 +89287,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89319,7 +89319,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89351,7 +89351,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89383,7 +89383,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89415,7 +89415,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89447,7 +89447,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89479,7 +89479,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89511,7 +89511,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89543,7 +89543,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89575,7 +89575,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89607,7 +89607,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89639,7 +89639,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89671,7 +89671,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89703,7 +89703,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89735,7 +89735,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89767,7 +89767,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89799,7 +89799,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89831,7 +89831,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89863,7 +89863,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89895,7 +89895,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89927,7 +89927,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89959,7 +89959,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -89991,7 +89991,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -90023,7 +90023,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -90055,7 +90055,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -90087,7 +90087,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -90119,7 +90119,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -90151,7 +90151,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -90183,7 +90183,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -90215,7 +90215,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -90247,7 +90247,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>
@@ -90279,7 +90279,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>New Transfer</t>
+          <t>Previous Transfer</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_attendance.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_attendance.xlsx
@@ -41,7 +41,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +65,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003388D5"/>
+        <fgColor rgb="00FFF1A6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF1A6"/>
+        <fgColor rgb="00FFB97D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003388D5"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -121,7 +126,10 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -497,7 +505,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -5288,7 +5296,7 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -5305,10 +5313,10 @@
         <v>19</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>27</v>
@@ -5320,7 +5328,7 @@
         <v>2</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" s="7" t="n">
         <v>27</v>
@@ -5334,10 +5342,8 @@
       <c r="S32" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T32" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U32" s="7" t="inlineStr">
         <is>
@@ -5486,7 +5492,7 @@
           <t>200302@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -5505,10 +5511,10 @@
         <v>20</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>27</v>
@@ -5520,7 +5526,7 @@
         <v>1</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P33" s="7" t="n">
         <v>27</v>
@@ -5534,10 +5540,8 @@
       <c r="S33" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T33" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U33" s="7" t="inlineStr">
         <is>
@@ -5688,7 +5692,7 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -5705,10 +5709,10 @@
         <v>19</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>27</v>
@@ -5720,7 +5724,7 @@
         <v>2</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" s="7" t="n">
         <v>27</v>
@@ -5734,10 +5738,8 @@
       <c r="S34" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T34" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T34" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U34" s="7" t="inlineStr">
         <is>
@@ -5888,7 +5890,7 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -5905,10 +5907,10 @@
         <v>21</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>27</v>
@@ -5920,7 +5922,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P35" s="7" t="n">
         <v>27</v>
@@ -5934,10 +5936,8 @@
       <c r="S35" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T35" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U35" s="7" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
           <t>211139@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -6105,10 +6105,10 @@
         <v>20</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>27</v>
@@ -6120,7 +6120,7 @@
         <v>1</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P36" s="7" t="n">
         <v>27</v>
@@ -6134,10 +6134,8 @@
       <c r="S36" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T36" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T36" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U36" s="7" t="inlineStr">
         <is>
@@ -6288,7 +6286,7 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -6305,10 +6303,10 @@
         <v>21</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>27</v>
@@ -6320,7 +6318,7 @@
         <v>0</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P37" s="7" t="n">
         <v>27</v>
@@ -6334,10 +6332,8 @@
       <c r="S37" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T37" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T37" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U37" s="7" t="inlineStr">
         <is>
@@ -6488,7 +6484,7 @@
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -6505,10 +6501,10 @@
         <v>21</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>27</v>
@@ -6520,7 +6516,7 @@
         <v>0</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P38" s="7" t="n">
         <v>27</v>
@@ -6534,10 +6530,8 @@
       <c r="S38" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T38" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U38" s="7" t="inlineStr">
         <is>
@@ -6688,7 +6682,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -6705,10 +6699,10 @@
         <v>19</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>27</v>
@@ -6720,7 +6714,7 @@
         <v>2</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" s="7" t="n">
         <v>27</v>
@@ -6734,10 +6728,8 @@
       <c r="S39" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T39" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U39" s="7" t="inlineStr">
         <is>
@@ -6888,7 +6880,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -6905,10 +6897,10 @@
         <v>19</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>27</v>
@@ -6920,7 +6912,7 @@
         <v>2</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" s="7" t="n">
         <v>27</v>
@@ -6934,10 +6926,8 @@
       <c r="S40" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T40" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U40" s="7" t="inlineStr">
         <is>
@@ -7088,7 +7078,7 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -7105,10 +7095,10 @@
         <v>21</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L41" s="6" t="n">
         <v>27</v>
@@ -7120,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P41" s="7" t="n">
         <v>27</v>
@@ -7134,10 +7124,8 @@
       <c r="S41" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T41" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U41" s="7" t="inlineStr">
         <is>
@@ -7288,7 +7276,7 @@
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -7305,10 +7293,10 @@
         <v>21</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="6" t="n">
         <v>27</v>
@@ -7320,7 +7308,7 @@
         <v>0</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P42" s="7" t="n">
         <v>27</v>
@@ -7334,10 +7322,8 @@
       <c r="S42" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T42" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U42" s="7" t="inlineStr">
         <is>
@@ -7486,7 +7472,7 @@
           <t>220494@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -7505,10 +7491,10 @@
         <v>20</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L43" s="6" t="n">
         <v>27</v>
@@ -7520,7 +7506,7 @@
         <v>1</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P43" s="7" t="n">
         <v>27</v>
@@ -7534,10 +7520,8 @@
       <c r="S43" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T43" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T43" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U43" s="7" t="inlineStr">
         <is>
@@ -7686,7 +7670,7 @@
           <t>220501@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -7705,10 +7689,10 @@
         <v>20</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>27</v>
@@ -7720,7 +7704,7 @@
         <v>1</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P44" s="7" t="n">
         <v>27</v>
@@ -7734,10 +7718,8 @@
       <c r="S44" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T44" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T44" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U44" s="7" t="inlineStr">
         <is>
@@ -7886,7 +7868,7 @@
           <t>220516@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -7905,10 +7887,10 @@
         <v>20</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" s="6" t="n">
         <v>27</v>
@@ -7920,7 +7902,7 @@
         <v>1</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P45" s="7" t="n">
         <v>27</v>
@@ -7934,10 +7916,8 @@
       <c r="S45" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T45" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U45" s="7" t="inlineStr">
         <is>
@@ -8086,7 +8066,7 @@
           <t>220537@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -8105,10 +8085,10 @@
         <v>20</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>27</v>
@@ -8120,7 +8100,7 @@
         <v>1</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P46" s="7" t="n">
         <v>27</v>
@@ -8134,10 +8114,8 @@
       <c r="S46" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T46" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T46" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U46" s="7" t="inlineStr">
         <is>
@@ -8286,7 +8264,7 @@
           <t>220550@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -8305,10 +8283,10 @@
         <v>20</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L47" s="6" t="n">
         <v>27</v>
@@ -8320,7 +8298,7 @@
         <v>1</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P47" s="7" t="n">
         <v>27</v>
@@ -8334,10 +8312,8 @@
       <c r="S47" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T47" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U47" s="7" t="inlineStr">
         <is>
@@ -8486,7 +8462,7 @@
           <t>220577@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -8505,10 +8481,10 @@
         <v>20</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>27</v>
@@ -8520,7 +8496,7 @@
         <v>1</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P48" s="7" t="n">
         <v>27</v>
@@ -8534,10 +8510,8 @@
       <c r="S48" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T48" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T48" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U48" s="7" t="inlineStr">
         <is>
@@ -8686,7 +8660,7 @@
           <t>220615@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -8705,10 +8679,10 @@
         <v>20</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L49" s="6" t="n">
         <v>27</v>
@@ -8720,7 +8694,7 @@
         <v>1</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P49" s="7" t="n">
         <v>27</v>
@@ -8734,10 +8708,8 @@
       <c r="S49" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T49" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U49" s="7" t="inlineStr">
         <is>
@@ -8888,7 +8860,7 @@
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -8905,10 +8877,10 @@
         <v>21</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L50" s="6" t="n">
         <v>27</v>
@@ -8920,7 +8892,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P50" s="7" t="n">
         <v>27</v>
@@ -8934,10 +8906,8 @@
       <c r="S50" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T50" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U50" s="7" t="inlineStr">
         <is>
@@ -9088,7 +9058,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -9105,10 +9075,10 @@
         <v>19</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" s="6" t="n">
         <v>27</v>
@@ -9120,7 +9090,7 @@
         <v>2</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51" s="7" t="n">
         <v>27</v>
@@ -9134,10 +9104,8 @@
       <c r="S51" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T51" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U51" s="7" t="inlineStr">
         <is>
@@ -9288,7 +9256,7 @@
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -9305,10 +9273,10 @@
         <v>21</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>27</v>
@@ -9320,7 +9288,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P52" s="7" t="n">
         <v>27</v>
@@ -9334,10 +9302,8 @@
       <c r="S52" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T52" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T52" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U52" s="7" t="inlineStr">
         <is>
@@ -9488,7 +9454,7 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -9505,10 +9471,10 @@
         <v>19</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>27</v>
@@ -9520,7 +9486,7 @@
         <v>2</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53" s="7" t="n">
         <v>27</v>
@@ -9534,10 +9500,8 @@
       <c r="S53" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T53" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U53" s="7" t="inlineStr">
         <is>
@@ -9688,7 +9652,7 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -9705,10 +9669,10 @@
         <v>19</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L54" s="6" t="n">
         <v>27</v>
@@ -9720,7 +9684,7 @@
         <v>2</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" s="7" t="n">
         <v>27</v>
@@ -9734,10 +9698,8 @@
       <c r="S54" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T54" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U54" s="7" t="inlineStr">
         <is>
@@ -9886,7 +9848,7 @@
           <t>220628@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -9905,10 +9867,10 @@
         <v>20</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>27</v>
@@ -9920,7 +9882,7 @@
         <v>1</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P55" s="7" t="n">
         <v>27</v>
@@ -9934,10 +9896,8 @@
       <c r="S55" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T55" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U55" s="7" t="inlineStr">
         <is>
@@ -10088,7 +10048,7 @@
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -10105,10 +10065,10 @@
         <v>21</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L56" s="6" t="n">
         <v>27</v>
@@ -10120,7 +10080,7 @@
         <v>0</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P56" s="7" t="n">
         <v>27</v>
@@ -10134,10 +10094,8 @@
       <c r="S56" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T56" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U56" s="7" t="inlineStr">
         <is>
@@ -10286,7 +10244,7 @@
           <t>220630@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F57" s="9" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -10305,10 +10263,10 @@
         <v>20</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L57" s="6" t="n">
         <v>27</v>
@@ -10320,7 +10278,7 @@
         <v>1</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P57" s="7" t="n">
         <v>27</v>
@@ -10334,10 +10292,8 @@
       <c r="S57" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T57" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U57" s="7" t="inlineStr">
         <is>
@@ -10486,7 +10442,7 @@
           <t>220635@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F58" s="9" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -10505,10 +10461,10 @@
         <v>20</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L58" s="6" t="n">
         <v>27</v>
@@ -10520,7 +10476,7 @@
         <v>1</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P58" s="7" t="n">
         <v>27</v>
@@ -10534,10 +10490,8 @@
       <c r="S58" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T58" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U58" s="7" t="inlineStr">
         <is>
@@ -10688,7 +10642,7 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -10705,10 +10659,10 @@
         <v>21</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>27</v>
@@ -10720,7 +10674,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P59" s="7" t="n">
         <v>27</v>
@@ -10734,10 +10688,8 @@
       <c r="S59" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T59" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U59" s="7" t="inlineStr">
         <is>
@@ -10886,7 +10838,7 @@
           <t>220639@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F60" s="9" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -10905,10 +10857,10 @@
         <v>20</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L60" s="6" t="n">
         <v>27</v>
@@ -10920,7 +10872,7 @@
         <v>1</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P60" s="7" t="n">
         <v>27</v>
@@ -10934,10 +10886,8 @@
       <c r="S60" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T60" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T60" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U60" s="7" t="inlineStr">
         <is>
@@ -11088,7 +11038,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -11105,10 +11055,10 @@
         <v>19</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L61" s="6" t="n">
         <v>27</v>
@@ -11120,7 +11070,7 @@
         <v>2</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P61" s="7" t="n">
         <v>27</v>
@@ -11134,10 +11084,8 @@
       <c r="S61" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T61" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U61" s="7" t="inlineStr">
         <is>
@@ -11286,7 +11234,7 @@
           <t>220646@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F62" s="9" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -11305,10 +11253,10 @@
         <v>20</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>27</v>
@@ -11320,7 +11268,7 @@
         <v>1</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P62" s="7" t="n">
         <v>27</v>
@@ -11334,10 +11282,8 @@
       <c r="S62" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T62" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U62" s="7" t="inlineStr">
         <is>
@@ -11486,7 +11432,7 @@
           <t>220647@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -11505,10 +11451,10 @@
         <v>20</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63" s="6" t="n">
         <v>27</v>
@@ -11520,7 +11466,7 @@
         <v>1</v>
       </c>
       <c r="O63" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P63" s="7" t="n">
         <v>27</v>
@@ -11534,10 +11480,8 @@
       <c r="S63" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T63" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U63" s="7" t="inlineStr">
         <is>
@@ -11688,7 +11632,7 @@
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -11705,10 +11649,10 @@
         <v>19</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L64" s="6" t="n">
         <v>27</v>
@@ -11720,7 +11664,7 @@
         <v>2</v>
       </c>
       <c r="O64" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P64" s="7" t="n">
         <v>27</v>
@@ -11734,10 +11678,8 @@
       <c r="S64" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T64" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U64" s="7" t="inlineStr">
         <is>
@@ -11888,7 +11830,7 @@
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -11905,10 +11847,10 @@
         <v>19</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L65" s="6" t="n">
         <v>27</v>
@@ -11920,7 +11862,7 @@
         <v>2</v>
       </c>
       <c r="O65" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P65" s="7" t="n">
         <v>27</v>
@@ -11934,10 +11876,8 @@
       <c r="S65" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T65" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U65" s="7" t="inlineStr">
         <is>
@@ -12088,7 +12028,7 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -12105,10 +12045,10 @@
         <v>19</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L66" s="6" t="n">
         <v>27</v>
@@ -12120,7 +12060,7 @@
         <v>2</v>
       </c>
       <c r="O66" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P66" s="7" t="n">
         <v>27</v>
@@ -12134,10 +12074,8 @@
       <c r="S66" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T66" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U66" s="7" t="inlineStr">
         <is>
@@ -12288,7 +12226,7 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -12305,10 +12243,10 @@
         <v>21</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L67" s="6" t="n">
         <v>27</v>
@@ -12320,7 +12258,7 @@
         <v>0</v>
       </c>
       <c r="O67" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P67" s="7" t="n">
         <v>27</v>
@@ -12334,10 +12272,8 @@
       <c r="S67" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T67" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U67" s="7" t="inlineStr">
         <is>
@@ -12488,7 +12424,7 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -12505,10 +12441,10 @@
         <v>19</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L68" s="6" t="n">
         <v>27</v>
@@ -12520,7 +12456,7 @@
         <v>2</v>
       </c>
       <c r="O68" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P68" s="7" t="n">
         <v>27</v>
@@ -12534,10 +12470,8 @@
       <c r="S68" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T68" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U68" s="7" t="inlineStr">
         <is>
@@ -12686,7 +12620,7 @@
           <t>220659@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -12705,10 +12639,10 @@
         <v>20</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" s="6" t="n">
         <v>27</v>
@@ -12720,7 +12654,7 @@
         <v>1</v>
       </c>
       <c r="O69" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P69" s="7" t="n">
         <v>27</v>
@@ -12734,10 +12668,8 @@
       <c r="S69" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T69" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U69" s="7" t="inlineStr">
         <is>
@@ -12888,7 +12820,7 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -12905,10 +12837,10 @@
         <v>19</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L70" s="6" t="n">
         <v>27</v>
@@ -12920,7 +12852,7 @@
         <v>2</v>
       </c>
       <c r="O70" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P70" s="7" t="n">
         <v>27</v>
@@ -12934,10 +12866,8 @@
       <c r="S70" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T70" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U70" s="7" t="inlineStr">
         <is>
@@ -13088,7 +13018,7 @@
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -13105,10 +13035,10 @@
         <v>21</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L71" s="6" t="n">
         <v>27</v>
@@ -13120,7 +13050,7 @@
         <v>0</v>
       </c>
       <c r="O71" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P71" s="7" t="n">
         <v>27</v>
@@ -13134,10 +13064,8 @@
       <c r="S71" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T71" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U71" s="7" t="inlineStr">
         <is>
@@ -13288,7 +13216,7 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -13305,10 +13233,10 @@
         <v>21</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>27</v>
@@ -13320,7 +13248,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P72" s="7" t="n">
         <v>27</v>
@@ -13334,10 +13262,8 @@
       <c r="S72" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T72" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U72" s="7" t="inlineStr">
         <is>
@@ -13486,7 +13412,7 @@
           <t>220667@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr">
+      <c r="F73" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -13505,10 +13431,10 @@
         <v>20</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L73" s="6" t="n">
         <v>27</v>
@@ -13520,7 +13446,7 @@
         <v>1</v>
       </c>
       <c r="O73" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P73" s="7" t="n">
         <v>27</v>
@@ -13534,10 +13460,8 @@
       <c r="S73" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T73" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U73" s="7" t="inlineStr">
         <is>
@@ -13686,7 +13610,7 @@
           <t>220669@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F74" s="9" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -13705,10 +13629,10 @@
         <v>20</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L74" s="6" t="n">
         <v>27</v>
@@ -13720,7 +13644,7 @@
         <v>1</v>
       </c>
       <c r="O74" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P74" s="7" t="n">
         <v>27</v>
@@ -13734,10 +13658,8 @@
       <c r="S74" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T74" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U74" s="7" t="inlineStr">
         <is>
@@ -13888,7 +13810,7 @@
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -13905,10 +13827,10 @@
         <v>21</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L75" s="6" t="n">
         <v>27</v>
@@ -13920,7 +13842,7 @@
         <v>0</v>
       </c>
       <c r="O75" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P75" s="7" t="n">
         <v>27</v>
@@ -13934,10 +13856,8 @@
       <c r="S75" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T75" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U75" s="7" t="inlineStr">
         <is>
@@ -14088,7 +14008,7 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -14105,10 +14025,10 @@
         <v>21</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L76" s="6" t="n">
         <v>27</v>
@@ -14120,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="O76" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P76" s="7" t="n">
         <v>27</v>
@@ -14134,10 +14054,8 @@
       <c r="S76" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T76" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U76" s="7" t="inlineStr">
         <is>
@@ -14288,7 +14206,7 @@
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -14305,10 +14223,10 @@
         <v>19</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L77" s="6" t="n">
         <v>27</v>
@@ -14320,7 +14238,7 @@
         <v>2</v>
       </c>
       <c r="O77" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P77" s="7" t="n">
         <v>27</v>
@@ -14334,10 +14252,8 @@
       <c r="S77" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T77" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U77" s="7" t="inlineStr">
         <is>
@@ -14488,7 +14404,7 @@
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -14505,10 +14421,10 @@
         <v>19</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L78" s="6" t="n">
         <v>27</v>
@@ -14520,7 +14436,7 @@
         <v>2</v>
       </c>
       <c r="O78" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P78" s="7" t="n">
         <v>27</v>
@@ -14534,10 +14450,8 @@
       <c r="S78" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T78" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U78" s="7" t="inlineStr">
         <is>
@@ -14688,7 +14602,7 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -14705,10 +14619,10 @@
         <v>21</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L79" s="6" t="n">
         <v>27</v>
@@ -14720,7 +14634,7 @@
         <v>0</v>
       </c>
       <c r="O79" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P79" s="7" t="n">
         <v>27</v>
@@ -14734,10 +14648,8 @@
       <c r="S79" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T79" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U79" s="7" t="inlineStr">
         <is>
@@ -14888,7 +14800,7 @@
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -14905,10 +14817,10 @@
         <v>19</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L80" s="6" t="n">
         <v>27</v>
@@ -14920,7 +14832,7 @@
         <v>2</v>
       </c>
       <c r="O80" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P80" s="7" t="n">
         <v>27</v>
@@ -14934,10 +14846,8 @@
       <c r="S80" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T80" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T80" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U80" s="7" t="inlineStr">
         <is>
@@ -15088,7 +14998,7 @@
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -15105,10 +15015,10 @@
         <v>19</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L81" s="6" t="n">
         <v>27</v>
@@ -15120,7 +15030,7 @@
         <v>2</v>
       </c>
       <c r="O81" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P81" s="7" t="n">
         <v>27</v>
@@ -15134,10 +15044,8 @@
       <c r="S81" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T81" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T81" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U81" s="7" t="inlineStr">
         <is>
@@ -15288,7 +15196,7 @@
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -15305,10 +15213,10 @@
         <v>21</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L82" s="6" t="n">
         <v>27</v>
@@ -15320,7 +15228,7 @@
         <v>0</v>
       </c>
       <c r="O82" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P82" s="7" t="n">
         <v>27</v>
@@ -15334,10 +15242,8 @@
       <c r="S82" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T82" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T82" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U82" s="7" t="inlineStr">
         <is>
@@ -15488,7 +15394,7 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -15505,10 +15411,10 @@
         <v>21</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L83" s="6" t="n">
         <v>27</v>
@@ -15520,7 +15426,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P83" s="7" t="n">
         <v>27</v>
@@ -15534,10 +15440,8 @@
       <c r="S83" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T83" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U83" s="7" t="inlineStr">
         <is>
@@ -15688,7 +15592,7 @@
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -15705,10 +15609,10 @@
         <v>21</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L84" s="6" t="n">
         <v>27</v>
@@ -15720,7 +15624,7 @@
         <v>0</v>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P84" s="7" t="n">
         <v>27</v>
@@ -15734,10 +15638,8 @@
       <c r="S84" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T84" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U84" s="7" t="inlineStr">
         <is>
@@ -15888,7 +15790,7 @@
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -15905,10 +15807,10 @@
         <v>19</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L85" s="6" t="n">
         <v>27</v>
@@ -15920,7 +15822,7 @@
         <v>2</v>
       </c>
       <c r="O85" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P85" s="7" t="n">
         <v>27</v>
@@ -15934,10 +15836,8 @@
       <c r="S85" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T85" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U85" s="7" t="inlineStr">
         <is>
@@ -16088,7 +15988,7 @@
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -16105,10 +16005,10 @@
         <v>19</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L86" s="6" t="n">
         <v>27</v>
@@ -16120,7 +16020,7 @@
         <v>2</v>
       </c>
       <c r="O86" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" s="7" t="n">
         <v>27</v>
@@ -16134,10 +16034,8 @@
       <c r="S86" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T86" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="7" t="inlineStr">
         <is>
@@ -16288,7 +16186,7 @@
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -16305,10 +16203,10 @@
         <v>19</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L87" s="6" t="n">
         <v>27</v>
@@ -16320,7 +16218,7 @@
         <v>2</v>
       </c>
       <c r="O87" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87" s="7" t="n">
         <v>27</v>
@@ -16334,10 +16232,8 @@
       <c r="S87" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T87" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T87" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U87" s="7" t="inlineStr">
         <is>
@@ -16488,7 +16384,7 @@
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -16505,10 +16401,10 @@
         <v>19</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L88" s="6" t="n">
         <v>27</v>
@@ -16520,7 +16416,7 @@
         <v>2</v>
       </c>
       <c r="O88" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P88" s="7" t="n">
         <v>27</v>
@@ -16534,10 +16430,8 @@
       <c r="S88" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T88" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U88" s="7" t="inlineStr">
         <is>
@@ -16688,7 +16582,7 @@
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -16705,10 +16599,10 @@
         <v>21</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>27</v>
@@ -16720,7 +16614,7 @@
         <v>0</v>
       </c>
       <c r="O89" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P89" s="7" t="n">
         <v>27</v>
@@ -16734,10 +16628,8 @@
       <c r="S89" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T89" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T89" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U89" s="7" t="inlineStr">
         <is>
@@ -16888,7 +16780,7 @@
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -16905,10 +16797,10 @@
         <v>19</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>27</v>
@@ -16920,7 +16812,7 @@
         <v>2</v>
       </c>
       <c r="O90" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P90" s="7" t="n">
         <v>27</v>
@@ -16934,10 +16826,8 @@
       <c r="S90" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T90" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T90" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U90" s="7" t="inlineStr">
         <is>
@@ -17086,7 +16976,7 @@
           <t>220693@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -17105,10 +16995,10 @@
         <v>20</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K91" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L91" s="6" t="n">
         <v>27</v>
@@ -17120,7 +17010,7 @@
         <v>1</v>
       </c>
       <c r="O91" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P91" s="7" t="n">
         <v>27</v>
@@ -17134,10 +17024,8 @@
       <c r="S91" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T91" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T91" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U91" s="7" t="inlineStr">
         <is>
@@ -17288,7 +17176,7 @@
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -17305,10 +17193,10 @@
         <v>19</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>27</v>
@@ -17320,7 +17208,7 @@
         <v>2</v>
       </c>
       <c r="O92" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P92" s="7" t="n">
         <v>27</v>
@@ -17334,10 +17222,8 @@
       <c r="S92" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T92" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U92" s="7" t="inlineStr">
         <is>
@@ -17488,7 +17374,7 @@
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -17505,10 +17391,10 @@
         <v>21</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K93" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L93" s="6" t="n">
         <v>27</v>
@@ -17520,7 +17406,7 @@
         <v>0</v>
       </c>
       <c r="O93" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P93" s="7" t="n">
         <v>27</v>
@@ -17534,10 +17420,8 @@
       <c r="S93" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T93" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T93" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U93" s="7" t="inlineStr">
         <is>
@@ -17688,7 +17572,7 @@
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -17705,10 +17589,10 @@
         <v>21</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L94" s="6" t="n">
         <v>27</v>
@@ -17720,7 +17604,7 @@
         <v>0</v>
       </c>
       <c r="O94" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P94" s="7" t="n">
         <v>27</v>
@@ -17734,10 +17618,8 @@
       <c r="S94" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T94" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U94" s="7" t="inlineStr">
         <is>
@@ -17888,7 +17770,7 @@
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -17905,10 +17787,10 @@
         <v>19</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K95" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L95" s="6" t="n">
         <v>27</v>
@@ -17920,7 +17802,7 @@
         <v>2</v>
       </c>
       <c r="O95" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P95" s="7" t="n">
         <v>27</v>
@@ -17934,10 +17816,8 @@
       <c r="S95" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T95" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T95" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U95" s="7" t="inlineStr">
         <is>
@@ -18088,7 +17968,7 @@
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -18105,10 +17985,10 @@
         <v>19</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L96" s="6" t="n">
         <v>27</v>
@@ -18120,7 +18000,7 @@
         <v>2</v>
       </c>
       <c r="O96" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96" s="7" t="n">
         <v>27</v>
@@ -18134,10 +18014,8 @@
       <c r="S96" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T96" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T96" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U96" s="7" t="inlineStr">
         <is>
@@ -18288,7 +18166,7 @@
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -18305,10 +18183,10 @@
         <v>19</v>
       </c>
       <c r="J97" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K97" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L97" s="6" t="n">
         <v>27</v>
@@ -18320,7 +18198,7 @@
         <v>2</v>
       </c>
       <c r="O97" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P97" s="7" t="n">
         <v>27</v>
@@ -18334,10 +18212,8 @@
       <c r="S97" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T97" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T97" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U97" s="7" t="inlineStr">
         <is>
@@ -18488,7 +18364,7 @@
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -18505,10 +18381,10 @@
         <v>19</v>
       </c>
       <c r="J98" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L98" s="6" t="n">
         <v>27</v>
@@ -18520,7 +18396,7 @@
         <v>2</v>
       </c>
       <c r="O98" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P98" s="7" t="n">
         <v>27</v>
@@ -18534,10 +18410,8 @@
       <c r="S98" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T98" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T98" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U98" s="7" t="inlineStr">
         <is>
@@ -18688,7 +18562,7 @@
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -18705,10 +18579,10 @@
         <v>21</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K99" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L99" s="6" t="n">
         <v>27</v>
@@ -18720,7 +18594,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P99" s="7" t="n">
         <v>27</v>
@@ -18734,10 +18608,8 @@
       <c r="S99" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T99" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U99" s="7" t="inlineStr">
         <is>
@@ -18888,7 +18760,7 @@
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -18905,10 +18777,10 @@
         <v>19</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L100" s="6" t="n">
         <v>27</v>
@@ -18920,7 +18792,7 @@
         <v>2</v>
       </c>
       <c r="O100" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P100" s="7" t="n">
         <v>27</v>
@@ -18934,10 +18806,8 @@
       <c r="S100" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T100" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T100" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U100" s="7" t="inlineStr">
         <is>
@@ -19086,7 +18956,7 @@
           <t>220708@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr">
+      <c r="F101" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -19105,10 +18975,10 @@
         <v>20</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K101" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L101" s="6" t="n">
         <v>27</v>
@@ -19120,7 +18990,7 @@
         <v>1</v>
       </c>
       <c r="O101" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P101" s="7" t="n">
         <v>27</v>
@@ -19134,10 +19004,8 @@
       <c r="S101" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T101" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T101" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U101" s="7" t="inlineStr">
         <is>
@@ -19288,7 +19156,7 @@
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -19305,10 +19173,10 @@
         <v>19</v>
       </c>
       <c r="J102" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K102" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L102" s="6" t="n">
         <v>27</v>
@@ -19320,7 +19188,7 @@
         <v>2</v>
       </c>
       <c r="O102" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P102" s="7" t="n">
         <v>27</v>
@@ -19334,10 +19202,8 @@
       <c r="S102" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T102" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T102" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U102" s="7" t="inlineStr">
         <is>
@@ -19486,7 +19352,7 @@
           <t>220710@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F103" s="9" t="inlineStr">
+      <c r="F103" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -19505,10 +19371,10 @@
         <v>20</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K103" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L103" s="6" t="n">
         <v>27</v>
@@ -19520,7 +19386,7 @@
         <v>1</v>
       </c>
       <c r="O103" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P103" s="7" t="n">
         <v>27</v>
@@ -19534,10 +19400,8 @@
       <c r="S103" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T103" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U103" s="7" t="inlineStr">
         <is>
@@ -19688,7 +19552,7 @@
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -19705,10 +19569,10 @@
         <v>19</v>
       </c>
       <c r="J104" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K104" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L104" s="6" t="n">
         <v>27</v>
@@ -19720,7 +19584,7 @@
         <v>2</v>
       </c>
       <c r="O104" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P104" s="7" t="n">
         <v>27</v>
@@ -19734,10 +19598,8 @@
       <c r="S104" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T104" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T104" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U104" s="7" t="inlineStr">
         <is>
@@ -19888,7 +19750,7 @@
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -19905,10 +19767,10 @@
         <v>19</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K105" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L105" s="6" t="n">
         <v>27</v>
@@ -19920,7 +19782,7 @@
         <v>2</v>
       </c>
       <c r="O105" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P105" s="7" t="n">
         <v>27</v>
@@ -19934,10 +19796,8 @@
       <c r="S105" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T105" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U105" s="7" t="inlineStr">
         <is>
@@ -20088,7 +19948,7 @@
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -20105,10 +19965,10 @@
         <v>19</v>
       </c>
       <c r="J106" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K106" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L106" s="6" t="n">
         <v>27</v>
@@ -20120,7 +19980,7 @@
         <v>2</v>
       </c>
       <c r="O106" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P106" s="7" t="n">
         <v>27</v>
@@ -20134,10 +19994,8 @@
       <c r="S106" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T106" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T106" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U106" s="7" t="inlineStr">
         <is>
@@ -20288,7 +20146,7 @@
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -20305,10 +20163,10 @@
         <v>19</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K107" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L107" s="6" t="n">
         <v>27</v>
@@ -20320,7 +20178,7 @@
         <v>2</v>
       </c>
       <c r="O107" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P107" s="7" t="n">
         <v>27</v>
@@ -20334,10 +20192,8 @@
       <c r="S107" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T107" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T107" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U107" s="7" t="inlineStr">
         <is>
@@ -20488,7 +20344,7 @@
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -20505,10 +20361,10 @@
         <v>19</v>
       </c>
       <c r="J108" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K108" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L108" s="6" t="n">
         <v>27</v>
@@ -20520,7 +20376,7 @@
         <v>2</v>
       </c>
       <c r="O108" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P108" s="7" t="n">
         <v>27</v>
@@ -20534,10 +20390,8 @@
       <c r="S108" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T108" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T108" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U108" s="7" t="inlineStr">
         <is>
@@ -20688,7 +20542,7 @@
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -20705,10 +20559,10 @@
         <v>21</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K109" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L109" s="6" t="n">
         <v>27</v>
@@ -20720,7 +20574,7 @@
         <v>0</v>
       </c>
       <c r="O109" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P109" s="7" t="n">
         <v>27</v>
@@ -20734,10 +20588,8 @@
       <c r="S109" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T109" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T109" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U109" s="7" t="inlineStr">
         <is>
@@ -20888,7 +20740,7 @@
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -20905,10 +20757,10 @@
         <v>19</v>
       </c>
       <c r="J110" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K110" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L110" s="6" t="n">
         <v>27</v>
@@ -20920,7 +20772,7 @@
         <v>2</v>
       </c>
       <c r="O110" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" s="7" t="n">
         <v>27</v>
@@ -20934,10 +20786,8 @@
       <c r="S110" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T110" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T110" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U110" s="7" t="inlineStr">
         <is>
@@ -21088,7 +20938,7 @@
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -21105,10 +20955,10 @@
         <v>19</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K111" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L111" s="6" t="n">
         <v>27</v>
@@ -21120,7 +20970,7 @@
         <v>2</v>
       </c>
       <c r="O111" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P111" s="7" t="n">
         <v>27</v>
@@ -21134,10 +20984,8 @@
       <c r="S111" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T111" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T111" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="7" t="inlineStr">
         <is>
@@ -21288,7 +21136,7 @@
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -21305,10 +21153,10 @@
         <v>19</v>
       </c>
       <c r="J112" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L112" s="6" t="n">
         <v>27</v>
@@ -21320,7 +21168,7 @@
         <v>2</v>
       </c>
       <c r="O112" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P112" s="7" t="n">
         <v>27</v>
@@ -21334,10 +21182,8 @@
       <c r="S112" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T112" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T112" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U112" s="7" t="inlineStr">
         <is>
@@ -21486,7 +21332,7 @@
           <t>220725@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F113" s="9" t="inlineStr">
+      <c r="F113" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -21505,10 +21351,10 @@
         <v>20</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K113" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L113" s="6" t="n">
         <v>27</v>
@@ -21520,7 +21366,7 @@
         <v>1</v>
       </c>
       <c r="O113" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P113" s="7" t="n">
         <v>27</v>
@@ -21534,10 +21380,8 @@
       <c r="S113" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T113" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T113" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U113" s="7" t="inlineStr">
         <is>
@@ -21688,7 +21532,7 @@
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -21705,10 +21549,10 @@
         <v>19</v>
       </c>
       <c r="J114" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K114" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L114" s="6" t="n">
         <v>27</v>
@@ -21720,7 +21564,7 @@
         <v>2</v>
       </c>
       <c r="O114" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P114" s="7" t="n">
         <v>27</v>
@@ -21734,10 +21578,8 @@
       <c r="S114" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T114" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T114" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U114" s="7" t="inlineStr">
         <is>
@@ -21888,7 +21730,7 @@
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -21905,10 +21747,10 @@
         <v>19</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K115" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L115" s="6" t="n">
         <v>27</v>
@@ -21920,7 +21762,7 @@
         <v>2</v>
       </c>
       <c r="O115" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P115" s="7" t="n">
         <v>27</v>
@@ -21934,10 +21776,8 @@
       <c r="S115" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T115" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T115" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U115" s="7" t="inlineStr">
         <is>
@@ -22088,7 +21928,7 @@
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -22105,10 +21945,10 @@
         <v>19</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K116" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L116" s="6" t="n">
         <v>27</v>
@@ -22120,7 +21960,7 @@
         <v>2</v>
       </c>
       <c r="O116" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P116" s="7" t="n">
         <v>27</v>
@@ -22134,10 +21974,8 @@
       <c r="S116" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T116" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T116" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U116" s="7" t="inlineStr">
         <is>
@@ -22288,7 +22126,7 @@
       </c>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -22305,10 +22143,10 @@
         <v>19</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K117" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L117" s="6" t="n">
         <v>27</v>
@@ -22320,7 +22158,7 @@
         <v>2</v>
       </c>
       <c r="O117" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P117" s="7" t="n">
         <v>27</v>
@@ -22334,10 +22172,8 @@
       <c r="S117" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T117" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T117" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U117" s="7" t="inlineStr">
         <is>
@@ -22488,7 +22324,7 @@
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -22505,10 +22341,10 @@
         <v>19</v>
       </c>
       <c r="J118" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L118" s="6" t="n">
         <v>27</v>
@@ -22520,7 +22356,7 @@
         <v>2</v>
       </c>
       <c r="O118" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P118" s="7" t="n">
         <v>27</v>
@@ -22534,10 +22370,8 @@
       <c r="S118" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T118" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T118" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U118" s="7" t="inlineStr">
         <is>
@@ -22688,7 +22522,7 @@
       </c>
       <c r="F119" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -22705,10 +22539,10 @@
         <v>19</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K119" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L119" s="6" t="n">
         <v>27</v>
@@ -22720,7 +22554,7 @@
         <v>2</v>
       </c>
       <c r="O119" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P119" s="7" t="n">
         <v>27</v>
@@ -22734,10 +22568,8 @@
       <c r="S119" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T119" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T119" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U119" s="7" t="inlineStr">
         <is>
@@ -22888,7 +22720,7 @@
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -22905,10 +22737,10 @@
         <v>19</v>
       </c>
       <c r="J120" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K120" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L120" s="6" t="n">
         <v>27</v>
@@ -22920,7 +22752,7 @@
         <v>2</v>
       </c>
       <c r="O120" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P120" s="7" t="n">
         <v>27</v>
@@ -22934,10 +22766,8 @@
       <c r="S120" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T120" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T120" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U120" s="7" t="inlineStr">
         <is>
@@ -23088,7 +22918,7 @@
       </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -23105,10 +22935,10 @@
         <v>19</v>
       </c>
       <c r="J121" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K121" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L121" s="6" t="n">
         <v>27</v>
@@ -23120,7 +22950,7 @@
         <v>2</v>
       </c>
       <c r="O121" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P121" s="7" t="n">
         <v>27</v>
@@ -23134,10 +22964,8 @@
       <c r="S121" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T121" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T121" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U121" s="7" t="inlineStr">
         <is>
@@ -23286,7 +23114,7 @@
           <t>220735@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F122" s="9" t="inlineStr">
+      <c r="F122" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -23305,10 +23133,10 @@
         <v>20</v>
       </c>
       <c r="J122" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K122" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L122" s="6" t="n">
         <v>27</v>
@@ -23320,7 +23148,7 @@
         <v>1</v>
       </c>
       <c r="O122" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P122" s="7" t="n">
         <v>27</v>
@@ -23334,10 +23162,8 @@
       <c r="S122" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T122" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T122" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U122" s="7" t="inlineStr">
         <is>
@@ -23488,7 +23314,7 @@
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -23505,10 +23331,10 @@
         <v>21</v>
       </c>
       <c r="J123" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K123" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L123" s="6" t="n">
         <v>27</v>
@@ -23520,7 +23346,7 @@
         <v>0</v>
       </c>
       <c r="O123" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P123" s="7" t="n">
         <v>27</v>
@@ -23534,10 +23360,8 @@
       <c r="S123" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T123" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T123" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U123" s="7" t="inlineStr">
         <is>
@@ -23688,7 +23512,7 @@
       </c>
       <c r="F124" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -23705,10 +23529,10 @@
         <v>19</v>
       </c>
       <c r="J124" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K124" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L124" s="6" t="n">
         <v>27</v>
@@ -23720,7 +23544,7 @@
         <v>2</v>
       </c>
       <c r="O124" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P124" s="7" t="n">
         <v>27</v>
@@ -23734,10 +23558,8 @@
       <c r="S124" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T124" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T124" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U124" s="7" t="inlineStr">
         <is>
@@ -23888,7 +23710,7 @@
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -23905,10 +23727,10 @@
         <v>19</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K125" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L125" s="6" t="n">
         <v>27</v>
@@ -23920,7 +23742,7 @@
         <v>2</v>
       </c>
       <c r="O125" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P125" s="7" t="n">
         <v>27</v>
@@ -23934,10 +23756,8 @@
       <c r="S125" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T125" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T125" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U125" s="7" t="inlineStr">
         <is>
@@ -24088,7 +23908,7 @@
       </c>
       <c r="F126" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -24105,10 +23925,10 @@
         <v>19</v>
       </c>
       <c r="J126" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K126" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L126" s="6" t="n">
         <v>27</v>
@@ -24120,7 +23940,7 @@
         <v>2</v>
       </c>
       <c r="O126" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P126" s="7" t="n">
         <v>27</v>
@@ -24134,10 +23954,8 @@
       <c r="S126" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T126" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T126" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U126" s="7" t="inlineStr">
         <is>
@@ -24288,7 +24106,7 @@
       </c>
       <c r="F127" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -24305,10 +24123,10 @@
         <v>19</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K127" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L127" s="6" t="n">
         <v>27</v>
@@ -24320,7 +24138,7 @@
         <v>2</v>
       </c>
       <c r="O127" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P127" s="7" t="n">
         <v>27</v>
@@ -24334,10 +24152,8 @@
       <c r="S127" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T127" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T127" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U127" s="7" t="inlineStr">
         <is>
@@ -24488,7 +24304,7 @@
       </c>
       <c r="F128" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -24505,10 +24321,10 @@
         <v>19</v>
       </c>
       <c r="J128" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K128" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L128" s="6" t="n">
         <v>27</v>
@@ -24520,7 +24336,7 @@
         <v>2</v>
       </c>
       <c r="O128" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P128" s="7" t="n">
         <v>27</v>
@@ -24534,10 +24350,8 @@
       <c r="S128" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T128" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T128" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U128" s="7" t="inlineStr">
         <is>
@@ -24688,7 +24502,7 @@
       </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -24705,10 +24519,10 @@
         <v>21</v>
       </c>
       <c r="J129" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K129" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L129" s="6" t="n">
         <v>27</v>
@@ -24720,7 +24534,7 @@
         <v>0</v>
       </c>
       <c r="O129" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P129" s="7" t="n">
         <v>27</v>
@@ -24734,10 +24548,8 @@
       <c r="S129" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T129" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T129" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U129" s="7" t="inlineStr">
         <is>
@@ -24888,7 +24700,7 @@
       </c>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -24905,10 +24717,10 @@
         <v>21</v>
       </c>
       <c r="J130" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K130" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L130" s="6" t="n">
         <v>27</v>
@@ -24920,7 +24732,7 @@
         <v>0</v>
       </c>
       <c r="O130" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P130" s="7" t="n">
         <v>27</v>
@@ -24934,10 +24746,8 @@
       <c r="S130" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T130" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T130" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U130" s="7" t="inlineStr">
         <is>
@@ -25086,7 +24896,7 @@
           <t>220748@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F131" s="9" t="inlineStr">
+      <c r="F131" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -25105,10 +24915,10 @@
         <v>20</v>
       </c>
       <c r="J131" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K131" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L131" s="6" t="n">
         <v>27</v>
@@ -25120,7 +24930,7 @@
         <v>1</v>
       </c>
       <c r="O131" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P131" s="7" t="n">
         <v>27</v>
@@ -25134,10 +24944,8 @@
       <c r="S131" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T131" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T131" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U131" s="7" t="inlineStr">
         <is>
@@ -25288,7 +25096,7 @@
       </c>
       <c r="F132" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -25305,10 +25113,10 @@
         <v>19</v>
       </c>
       <c r="J132" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K132" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L132" s="6" t="n">
         <v>27</v>
@@ -25320,7 +25128,7 @@
         <v>2</v>
       </c>
       <c r="O132" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P132" s="7" t="n">
         <v>27</v>
@@ -25334,10 +25142,8 @@
       <c r="S132" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T132" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T132" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U132" s="7" t="inlineStr">
         <is>
@@ -25488,7 +25294,7 @@
       </c>
       <c r="F133" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -25505,10 +25311,10 @@
         <v>19</v>
       </c>
       <c r="J133" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K133" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L133" s="6" t="n">
         <v>27</v>
@@ -25520,7 +25326,7 @@
         <v>2</v>
       </c>
       <c r="O133" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P133" s="7" t="n">
         <v>27</v>
@@ -25534,10 +25340,8 @@
       <c r="S133" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T133" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T133" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U133" s="7" t="inlineStr">
         <is>
@@ -25688,7 +25492,7 @@
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -25705,10 +25509,10 @@
         <v>19</v>
       </c>
       <c r="J134" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K134" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L134" s="6" t="n">
         <v>27</v>
@@ -25720,7 +25524,7 @@
         <v>2</v>
       </c>
       <c r="O134" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P134" s="7" t="n">
         <v>27</v>
@@ -25734,10 +25538,8 @@
       <c r="S134" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T134" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T134" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U134" s="7" t="inlineStr">
         <is>
@@ -25886,7 +25688,7 @@
           <t>220753@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F135" s="9" t="inlineStr">
+      <c r="F135" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -25905,10 +25707,10 @@
         <v>20</v>
       </c>
       <c r="J135" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K135" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L135" s="6" t="n">
         <v>27</v>
@@ -25920,7 +25722,7 @@
         <v>1</v>
       </c>
       <c r="O135" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P135" s="7" t="n">
         <v>27</v>
@@ -25934,10 +25736,8 @@
       <c r="S135" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T135" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T135" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U135" s="7" t="inlineStr">
         <is>
@@ -26088,7 +25888,7 @@
       </c>
       <c r="F136" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -26105,10 +25905,10 @@
         <v>19</v>
       </c>
       <c r="J136" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K136" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L136" s="6" t="n">
         <v>27</v>
@@ -26120,7 +25920,7 @@
         <v>2</v>
       </c>
       <c r="O136" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P136" s="7" t="n">
         <v>27</v>
@@ -26134,10 +25934,8 @@
       <c r="S136" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T136" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T136" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U136" s="7" t="inlineStr">
         <is>
@@ -26288,7 +26086,7 @@
       </c>
       <c r="F137" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -26305,10 +26103,10 @@
         <v>19</v>
       </c>
       <c r="J137" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K137" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L137" s="6" t="n">
         <v>27</v>
@@ -26320,7 +26118,7 @@
         <v>2</v>
       </c>
       <c r="O137" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P137" s="7" t="n">
         <v>27</v>
@@ -26334,10 +26132,8 @@
       <c r="S137" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T137" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T137" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U137" s="7" t="inlineStr">
         <is>
@@ -26488,7 +26284,7 @@
       </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -26505,10 +26301,10 @@
         <v>19</v>
       </c>
       <c r="J138" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K138" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L138" s="6" t="n">
         <v>27</v>
@@ -26520,7 +26316,7 @@
         <v>2</v>
       </c>
       <c r="O138" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P138" s="7" t="n">
         <v>27</v>
@@ -26534,10 +26330,8 @@
       <c r="S138" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T138" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T138" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U138" s="7" t="inlineStr">
         <is>
@@ -26686,7 +26480,7 @@
           <t>220758@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F139" s="9" t="inlineStr">
+      <c r="F139" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -26705,10 +26499,10 @@
         <v>20</v>
       </c>
       <c r="J139" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K139" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L139" s="6" t="n">
         <v>27</v>
@@ -26720,7 +26514,7 @@
         <v>1</v>
       </c>
       <c r="O139" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P139" s="7" t="n">
         <v>27</v>
@@ -26734,10 +26528,8 @@
       <c r="S139" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T139" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T139" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U139" s="7" t="inlineStr">
         <is>
@@ -26888,7 +26680,7 @@
       </c>
       <c r="F140" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -26905,10 +26697,10 @@
         <v>19</v>
       </c>
       <c r="J140" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K140" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L140" s="6" t="n">
         <v>27</v>
@@ -26920,7 +26712,7 @@
         <v>2</v>
       </c>
       <c r="O140" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P140" s="7" t="n">
         <v>27</v>
@@ -26934,10 +26726,8 @@
       <c r="S140" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T140" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T140" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U140" s="7" t="inlineStr">
         <is>
@@ -27088,7 +26878,7 @@
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -27105,10 +26895,10 @@
         <v>21</v>
       </c>
       <c r="J141" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K141" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L141" s="6" t="n">
         <v>27</v>
@@ -27120,7 +26910,7 @@
         <v>0</v>
       </c>
       <c r="O141" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P141" s="7" t="n">
         <v>27</v>
@@ -27134,10 +26924,8 @@
       <c r="S141" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T141" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T141" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U141" s="7" t="inlineStr">
         <is>
@@ -27286,7 +27074,7 @@
           <t>220762@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F142" s="9" t="inlineStr">
+      <c r="F142" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -27305,10 +27093,10 @@
         <v>20</v>
       </c>
       <c r="J142" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K142" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L142" s="6" t="n">
         <v>27</v>
@@ -27320,7 +27108,7 @@
         <v>1</v>
       </c>
       <c r="O142" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P142" s="7" t="n">
         <v>27</v>
@@ -27334,10 +27122,8 @@
       <c r="S142" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T142" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T142" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U142" s="7" t="inlineStr">
         <is>
@@ -27486,7 +27272,7 @@
           <t>220764@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F143" s="9" t="inlineStr">
+      <c r="F143" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -27505,10 +27291,10 @@
         <v>20</v>
       </c>
       <c r="J143" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K143" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L143" s="6" t="n">
         <v>27</v>
@@ -27520,7 +27306,7 @@
         <v>1</v>
       </c>
       <c r="O143" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P143" s="7" t="n">
         <v>27</v>
@@ -27534,10 +27320,8 @@
       <c r="S143" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T143" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T143" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U143" s="7" t="inlineStr">
         <is>
@@ -27688,7 +27472,7 @@
       </c>
       <c r="F144" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -27705,10 +27489,10 @@
         <v>19</v>
       </c>
       <c r="J144" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K144" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L144" s="6" t="n">
         <v>27</v>
@@ -27720,7 +27504,7 @@
         <v>2</v>
       </c>
       <c r="O144" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P144" s="7" t="n">
         <v>27</v>
@@ -27734,10 +27518,8 @@
       <c r="S144" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T144" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T144" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U144" s="7" t="inlineStr">
         <is>
@@ -27888,7 +27670,7 @@
       </c>
       <c r="F145" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -27905,10 +27687,10 @@
         <v>19</v>
       </c>
       <c r="J145" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K145" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L145" s="6" t="n">
         <v>27</v>
@@ -27920,7 +27702,7 @@
         <v>2</v>
       </c>
       <c r="O145" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P145" s="7" t="n">
         <v>27</v>
@@ -27934,10 +27716,8 @@
       <c r="S145" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T145" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T145" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U145" s="7" t="inlineStr">
         <is>
@@ -28086,7 +27866,7 @@
           <t>220772@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F146" s="9" t="inlineStr">
+      <c r="F146" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -28105,10 +27885,10 @@
         <v>20</v>
       </c>
       <c r="J146" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K146" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L146" s="6" t="n">
         <v>27</v>
@@ -28120,7 +27900,7 @@
         <v>1</v>
       </c>
       <c r="O146" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P146" s="7" t="n">
         <v>27</v>
@@ -28134,10 +27914,8 @@
       <c r="S146" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T146" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T146" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U146" s="7" t="inlineStr">
         <is>
@@ -28288,7 +28066,7 @@
       </c>
       <c r="F147" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -28305,10 +28083,10 @@
         <v>19</v>
       </c>
       <c r="J147" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K147" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L147" s="6" t="n">
         <v>27</v>
@@ -28320,7 +28098,7 @@
         <v>2</v>
       </c>
       <c r="O147" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P147" s="7" t="n">
         <v>27</v>
@@ -28334,10 +28112,8 @@
       <c r="S147" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T147" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T147" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U147" s="7" t="inlineStr">
         <is>
@@ -28488,7 +28264,7 @@
       </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -28505,10 +28281,10 @@
         <v>19</v>
       </c>
       <c r="J148" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K148" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L148" s="6" t="n">
         <v>27</v>
@@ -28520,7 +28296,7 @@
         <v>2</v>
       </c>
       <c r="O148" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P148" s="7" t="n">
         <v>27</v>
@@ -28534,10 +28310,8 @@
       <c r="S148" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T148" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T148" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U148" s="7" t="inlineStr">
         <is>
@@ -28688,7 +28462,7 @@
       </c>
       <c r="F149" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -28705,10 +28479,10 @@
         <v>19</v>
       </c>
       <c r="J149" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K149" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L149" s="6" t="n">
         <v>27</v>
@@ -28720,7 +28494,7 @@
         <v>2</v>
       </c>
       <c r="O149" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P149" s="7" t="n">
         <v>27</v>
@@ -28734,10 +28508,8 @@
       <c r="S149" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T149" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T149" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U149" s="7" t="inlineStr">
         <is>
@@ -28886,7 +28658,7 @@
           <t>220776@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F150" s="9" t="inlineStr">
+      <c r="F150" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -28905,10 +28677,10 @@
         <v>20</v>
       </c>
       <c r="J150" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K150" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L150" s="6" t="n">
         <v>27</v>
@@ -28920,7 +28692,7 @@
         <v>1</v>
       </c>
       <c r="O150" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P150" s="7" t="n">
         <v>27</v>
@@ -28934,10 +28706,8 @@
       <c r="S150" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T150" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T150" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U150" s="7" t="inlineStr">
         <is>
@@ -29088,7 +28858,7 @@
       </c>
       <c r="F151" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -29105,10 +28875,10 @@
         <v>21</v>
       </c>
       <c r="J151" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K151" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L151" s="6" t="n">
         <v>27</v>
@@ -29120,7 +28890,7 @@
         <v>0</v>
       </c>
       <c r="O151" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P151" s="7" t="n">
         <v>27</v>
@@ -29134,10 +28904,8 @@
       <c r="S151" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T151" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T151" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U151" s="7" t="inlineStr">
         <is>
@@ -29288,7 +29056,7 @@
       </c>
       <c r="F152" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -29305,10 +29073,10 @@
         <v>19</v>
       </c>
       <c r="J152" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K152" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L152" s="6" t="n">
         <v>27</v>
@@ -29320,7 +29088,7 @@
         <v>2</v>
       </c>
       <c r="O152" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P152" s="7" t="n">
         <v>27</v>
@@ -29334,10 +29102,8 @@
       <c r="S152" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T152" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T152" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U152" s="7" t="inlineStr">
         <is>
@@ -29486,7 +29252,7 @@
           <t>220779@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F153" s="9" t="inlineStr">
+      <c r="F153" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -29505,10 +29271,10 @@
         <v>20</v>
       </c>
       <c r="J153" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K153" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L153" s="6" t="n">
         <v>27</v>
@@ -29520,7 +29286,7 @@
         <v>1</v>
       </c>
       <c r="O153" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P153" s="7" t="n">
         <v>27</v>
@@ -29534,10 +29300,8 @@
       <c r="S153" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T153" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T153" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U153" s="7" t="inlineStr">
         <is>
@@ -29688,7 +29452,7 @@
       </c>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -29705,10 +29469,10 @@
         <v>21</v>
       </c>
       <c r="J154" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K154" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L154" s="6" t="n">
         <v>27</v>
@@ -29720,7 +29484,7 @@
         <v>0</v>
       </c>
       <c r="O154" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P154" s="7" t="n">
         <v>27</v>
@@ -29734,10 +29498,8 @@
       <c r="S154" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T154" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T154" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U154" s="7" t="inlineStr">
         <is>
@@ -29888,7 +29650,7 @@
       </c>
       <c r="F155" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -29905,10 +29667,10 @@
         <v>19</v>
       </c>
       <c r="J155" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K155" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L155" s="6" t="n">
         <v>27</v>
@@ -29920,7 +29682,7 @@
         <v>2</v>
       </c>
       <c r="O155" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P155" s="7" t="n">
         <v>27</v>
@@ -29934,10 +29696,8 @@
       <c r="S155" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T155" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T155" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U155" s="7" t="inlineStr">
         <is>
@@ -30088,7 +29848,7 @@
       </c>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -30105,10 +29865,10 @@
         <v>21</v>
       </c>
       <c r="J156" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K156" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L156" s="6" t="n">
         <v>27</v>
@@ -30120,7 +29880,7 @@
         <v>0</v>
       </c>
       <c r="O156" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P156" s="7" t="n">
         <v>27</v>
@@ -30134,10 +29894,8 @@
       <c r="S156" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T156" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T156" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U156" s="7" t="inlineStr">
         <is>
@@ -30288,7 +30046,7 @@
       </c>
       <c r="F157" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -30305,10 +30063,10 @@
         <v>21</v>
       </c>
       <c r="J157" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K157" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L157" s="6" t="n">
         <v>27</v>
@@ -30320,7 +30078,7 @@
         <v>0</v>
       </c>
       <c r="O157" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P157" s="7" t="n">
         <v>27</v>
@@ -30334,10 +30092,8 @@
       <c r="S157" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T157" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T157" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U157" s="7" t="inlineStr">
         <is>
@@ -30488,7 +30244,7 @@
       </c>
       <c r="F158" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -30505,10 +30261,10 @@
         <v>19</v>
       </c>
       <c r="J158" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K158" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L158" s="6" t="n">
         <v>27</v>
@@ -30520,7 +30276,7 @@
         <v>2</v>
       </c>
       <c r="O158" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P158" s="7" t="n">
         <v>27</v>
@@ -30534,10 +30290,8 @@
       <c r="S158" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T158" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T158" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U158" s="7" t="inlineStr">
         <is>
@@ -30688,7 +30442,7 @@
       </c>
       <c r="F159" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -30705,10 +30459,10 @@
         <v>19</v>
       </c>
       <c r="J159" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K159" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L159" s="6" t="n">
         <v>27</v>
@@ -30720,7 +30474,7 @@
         <v>2</v>
       </c>
       <c r="O159" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P159" s="7" t="n">
         <v>27</v>
@@ -30734,10 +30488,8 @@
       <c r="S159" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T159" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T159" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U159" s="7" t="inlineStr">
         <is>
@@ -30886,7 +30638,7 @@
           <t>220788@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F160" s="9" t="inlineStr">
+      <c r="F160" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -30905,10 +30657,10 @@
         <v>20</v>
       </c>
       <c r="J160" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K160" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L160" s="6" t="n">
         <v>27</v>
@@ -30920,7 +30672,7 @@
         <v>1</v>
       </c>
       <c r="O160" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P160" s="7" t="n">
         <v>27</v>
@@ -30934,10 +30686,8 @@
       <c r="S160" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T160" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T160" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U160" s="7" t="inlineStr">
         <is>
@@ -31086,7 +30836,7 @@
           <t>220789@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F161" s="9" t="inlineStr">
+      <c r="F161" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -31105,10 +30855,10 @@
         <v>20</v>
       </c>
       <c r="J161" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K161" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L161" s="6" t="n">
         <v>27</v>
@@ -31120,7 +30870,7 @@
         <v>1</v>
       </c>
       <c r="O161" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P161" s="7" t="n">
         <v>27</v>
@@ -31134,10 +30884,8 @@
       <c r="S161" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T161" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T161" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U161" s="7" t="inlineStr">
         <is>
@@ -31288,7 +31036,7 @@
       </c>
       <c r="F162" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -31305,10 +31053,10 @@
         <v>19</v>
       </c>
       <c r="J162" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K162" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L162" s="6" t="n">
         <v>27</v>
@@ -31320,7 +31068,7 @@
         <v>2</v>
       </c>
       <c r="O162" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P162" s="7" t="n">
         <v>27</v>
@@ -31334,10 +31082,8 @@
       <c r="S162" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T162" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T162" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U162" s="7" t="inlineStr">
         <is>
@@ -31486,7 +31232,7 @@
           <t>220791@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F163" s="9" t="inlineStr">
+      <c r="F163" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -31505,10 +31251,10 @@
         <v>20</v>
       </c>
       <c r="J163" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K163" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L163" s="6" t="n">
         <v>27</v>
@@ -31520,7 +31266,7 @@
         <v>1</v>
       </c>
       <c r="O163" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P163" s="7" t="n">
         <v>27</v>
@@ -31534,10 +31280,8 @@
       <c r="S163" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T163" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T163" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U163" s="7" t="inlineStr">
         <is>
@@ -31688,7 +31432,7 @@
       </c>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -31705,10 +31449,10 @@
         <v>21</v>
       </c>
       <c r="J164" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K164" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L164" s="6" t="n">
         <v>27</v>
@@ -31720,7 +31464,7 @@
         <v>0</v>
       </c>
       <c r="O164" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P164" s="7" t="n">
         <v>27</v>
@@ -31734,10 +31478,8 @@
       <c r="S164" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T164" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T164" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U164" s="7" t="inlineStr">
         <is>
@@ -31888,7 +31630,7 @@
       </c>
       <c r="F165" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -31905,10 +31647,10 @@
         <v>19</v>
       </c>
       <c r="J165" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K165" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L165" s="6" t="n">
         <v>27</v>
@@ -31920,7 +31662,7 @@
         <v>2</v>
       </c>
       <c r="O165" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P165" s="7" t="n">
         <v>27</v>
@@ -31934,10 +31676,8 @@
       <c r="S165" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T165" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T165" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U165" s="7" t="inlineStr">
         <is>
@@ -32086,7 +31826,7 @@
           <t>220794@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F166" s="9" t="inlineStr">
+      <c r="F166" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -32105,10 +31845,10 @@
         <v>20</v>
       </c>
       <c r="J166" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K166" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L166" s="6" t="n">
         <v>27</v>
@@ -32120,7 +31860,7 @@
         <v>1</v>
       </c>
       <c r="O166" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P166" s="7" t="n">
         <v>27</v>
@@ -32134,10 +31874,8 @@
       <c r="S166" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T166" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T166" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U166" s="7" t="inlineStr">
         <is>
@@ -32288,7 +32026,7 @@
       </c>
       <c r="F167" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -32305,10 +32043,10 @@
         <v>19</v>
       </c>
       <c r="J167" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K167" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L167" s="6" t="n">
         <v>27</v>
@@ -32320,7 +32058,7 @@
         <v>2</v>
       </c>
       <c r="O167" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P167" s="7" t="n">
         <v>27</v>
@@ -32334,10 +32072,8 @@
       <c r="S167" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T167" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T167" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U167" s="7" t="inlineStr">
         <is>
@@ -32486,7 +32222,7 @@
           <t>220796@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F168" s="9" t="inlineStr">
+      <c r="F168" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -32505,10 +32241,10 @@
         <v>20</v>
       </c>
       <c r="J168" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K168" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L168" s="6" t="n">
         <v>27</v>
@@ -32520,7 +32256,7 @@
         <v>1</v>
       </c>
       <c r="O168" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P168" s="7" t="n">
         <v>27</v>
@@ -32534,10 +32270,8 @@
       <c r="S168" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T168" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T168" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U168" s="7" t="inlineStr">
         <is>
@@ -32688,7 +32422,7 @@
       </c>
       <c r="F169" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -32705,10 +32439,10 @@
         <v>19</v>
       </c>
       <c r="J169" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K169" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L169" s="6" t="n">
         <v>27</v>
@@ -32720,7 +32454,7 @@
         <v>2</v>
       </c>
       <c r="O169" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P169" s="7" t="n">
         <v>27</v>
@@ -32734,10 +32468,8 @@
       <c r="S169" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T169" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T169" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U169" s="7" t="inlineStr">
         <is>
@@ -32888,7 +32620,7 @@
       </c>
       <c r="F170" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -32905,10 +32637,10 @@
         <v>19</v>
       </c>
       <c r="J170" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K170" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L170" s="6" t="n">
         <v>27</v>
@@ -32920,7 +32652,7 @@
         <v>2</v>
       </c>
       <c r="O170" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P170" s="7" t="n">
         <v>27</v>
@@ -32934,10 +32666,8 @@
       <c r="S170" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T170" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T170" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U170" s="7" t="inlineStr">
         <is>
@@ -33088,7 +32818,7 @@
       </c>
       <c r="F171" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -33105,10 +32835,10 @@
         <v>19</v>
       </c>
       <c r="J171" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K171" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L171" s="6" t="n">
         <v>27</v>
@@ -33120,7 +32850,7 @@
         <v>2</v>
       </c>
       <c r="O171" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P171" s="7" t="n">
         <v>27</v>
@@ -33134,10 +32864,8 @@
       <c r="S171" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T171" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T171" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U171" s="7" t="inlineStr">
         <is>
@@ -33288,7 +33016,7 @@
       </c>
       <c r="F172" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -33305,10 +33033,10 @@
         <v>19</v>
       </c>
       <c r="J172" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K172" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L172" s="6" t="n">
         <v>27</v>
@@ -33320,7 +33048,7 @@
         <v>2</v>
       </c>
       <c r="O172" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P172" s="7" t="n">
         <v>27</v>
@@ -33334,10 +33062,8 @@
       <c r="S172" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T172" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T172" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U172" s="7" t="inlineStr">
         <is>
@@ -33488,7 +33214,7 @@
       </c>
       <c r="F173" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -33505,10 +33231,10 @@
         <v>19</v>
       </c>
       <c r="J173" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K173" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L173" s="6" t="n">
         <v>27</v>
@@ -33520,7 +33246,7 @@
         <v>2</v>
       </c>
       <c r="O173" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P173" s="7" t="n">
         <v>27</v>
@@ -33534,10 +33260,8 @@
       <c r="S173" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T173" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T173" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U173" s="7" t="inlineStr">
         <is>
@@ -33688,7 +33412,7 @@
       </c>
       <c r="F174" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -33705,10 +33429,10 @@
         <v>19</v>
       </c>
       <c r="J174" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K174" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L174" s="6" t="n">
         <v>27</v>
@@ -33720,7 +33444,7 @@
         <v>2</v>
       </c>
       <c r="O174" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P174" s="7" t="n">
         <v>27</v>
@@ -33734,10 +33458,8 @@
       <c r="S174" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T174" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T174" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U174" s="7" t="inlineStr">
         <is>
@@ -33888,7 +33610,7 @@
       </c>
       <c r="F175" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -33905,10 +33627,10 @@
         <v>19</v>
       </c>
       <c r="J175" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K175" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L175" s="6" t="n">
         <v>27</v>
@@ -33920,7 +33642,7 @@
         <v>2</v>
       </c>
       <c r="O175" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P175" s="7" t="n">
         <v>27</v>
@@ -33934,10 +33656,8 @@
       <c r="S175" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T175" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T175" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U175" s="7" t="inlineStr">
         <is>
@@ -34086,7 +33806,7 @@
           <t>220805@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F176" s="9" t="inlineStr">
+      <c r="F176" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -34105,10 +33825,10 @@
         <v>20</v>
       </c>
       <c r="J176" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K176" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L176" s="6" t="n">
         <v>27</v>
@@ -34120,7 +33840,7 @@
         <v>1</v>
       </c>
       <c r="O176" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P176" s="7" t="n">
         <v>27</v>
@@ -34134,10 +33854,8 @@
       <c r="S176" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T176" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T176" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U176" s="7" t="inlineStr">
         <is>
@@ -34288,7 +34006,7 @@
       </c>
       <c r="F177" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -34305,10 +34023,10 @@
         <v>21</v>
       </c>
       <c r="J177" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K177" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L177" s="6" t="n">
         <v>27</v>
@@ -34320,7 +34038,7 @@
         <v>0</v>
       </c>
       <c r="O177" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P177" s="7" t="n">
         <v>27</v>
@@ -34334,10 +34052,8 @@
       <c r="S177" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T177" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T177" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U177" s="7" t="inlineStr">
         <is>
@@ -34488,7 +34204,7 @@
       </c>
       <c r="F178" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -34505,10 +34221,10 @@
         <v>21</v>
       </c>
       <c r="J178" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K178" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L178" s="6" t="n">
         <v>27</v>
@@ -34520,7 +34236,7 @@
         <v>0</v>
       </c>
       <c r="O178" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P178" s="7" t="n">
         <v>27</v>
@@ -34534,10 +34250,8 @@
       <c r="S178" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T178" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T178" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U178" s="7" t="inlineStr">
         <is>
@@ -34688,7 +34402,7 @@
       </c>
       <c r="F179" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -34705,10 +34419,10 @@
         <v>19</v>
       </c>
       <c r="J179" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K179" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L179" s="6" t="n">
         <v>27</v>
@@ -34720,7 +34434,7 @@
         <v>2</v>
       </c>
       <c r="O179" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P179" s="7" t="n">
         <v>27</v>
@@ -34734,10 +34448,8 @@
       <c r="S179" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T179" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T179" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U179" s="7" t="inlineStr">
         <is>
@@ -34888,7 +34600,7 @@
       </c>
       <c r="F180" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -34905,10 +34617,10 @@
         <v>19</v>
       </c>
       <c r="J180" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K180" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L180" s="6" t="n">
         <v>27</v>
@@ -34920,7 +34632,7 @@
         <v>2</v>
       </c>
       <c r="O180" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P180" s="7" t="n">
         <v>27</v>
@@ -34934,10 +34646,8 @@
       <c r="S180" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T180" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T180" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U180" s="7" t="inlineStr">
         <is>
@@ -35086,7 +34796,7 @@
           <t>220813@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F181" s="9" t="inlineStr">
+      <c r="F181" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -35105,10 +34815,10 @@
         <v>20</v>
       </c>
       <c r="J181" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K181" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L181" s="6" t="n">
         <v>27</v>
@@ -35120,7 +34830,7 @@
         <v>1</v>
       </c>
       <c r="O181" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P181" s="7" t="n">
         <v>27</v>
@@ -35134,10 +34844,8 @@
       <c r="S181" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T181" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T181" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U181" s="7" t="inlineStr">
         <is>
@@ -35288,7 +34996,7 @@
       </c>
       <c r="F182" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -35305,10 +35013,10 @@
         <v>21</v>
       </c>
       <c r="J182" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K182" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L182" s="6" t="n">
         <v>27</v>
@@ -35320,7 +35028,7 @@
         <v>0</v>
       </c>
       <c r="O182" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P182" s="7" t="n">
         <v>27</v>
@@ -35334,10 +35042,8 @@
       <c r="S182" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T182" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T182" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U182" s="7" t="inlineStr">
         <is>
@@ -35488,7 +35194,7 @@
       </c>
       <c r="F183" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -35505,10 +35211,10 @@
         <v>19</v>
       </c>
       <c r="J183" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K183" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L183" s="6" t="n">
         <v>27</v>
@@ -35520,7 +35226,7 @@
         <v>2</v>
       </c>
       <c r="O183" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P183" s="7" t="n">
         <v>27</v>
@@ -35534,10 +35240,8 @@
       <c r="S183" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T183" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T183" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U183" s="7" t="inlineStr">
         <is>
@@ -35688,7 +35392,7 @@
       </c>
       <c r="F184" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -35705,10 +35409,10 @@
         <v>19</v>
       </c>
       <c r="J184" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K184" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L184" s="6" t="n">
         <v>27</v>
@@ -35720,7 +35424,7 @@
         <v>2</v>
       </c>
       <c r="O184" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P184" s="7" t="n">
         <v>27</v>
@@ -35734,10 +35438,8 @@
       <c r="S184" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T184" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T184" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U184" s="7" t="inlineStr">
         <is>
@@ -35888,7 +35590,7 @@
       </c>
       <c r="F185" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -35905,10 +35607,10 @@
         <v>19</v>
       </c>
       <c r="J185" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K185" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L185" s="6" t="n">
         <v>27</v>
@@ -35920,7 +35622,7 @@
         <v>2</v>
       </c>
       <c r="O185" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P185" s="7" t="n">
         <v>27</v>
@@ -35934,10 +35636,8 @@
       <c r="S185" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T185" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T185" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U185" s="7" t="inlineStr">
         <is>
@@ -36088,7 +35788,7 @@
       </c>
       <c r="F186" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -36105,10 +35805,10 @@
         <v>19</v>
       </c>
       <c r="J186" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K186" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L186" s="6" t="n">
         <v>27</v>
@@ -36120,7 +35820,7 @@
         <v>2</v>
       </c>
       <c r="O186" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P186" s="7" t="n">
         <v>27</v>
@@ -36134,10 +35834,8 @@
       <c r="S186" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T186" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T186" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U186" s="7" t="inlineStr">
         <is>
@@ -36288,7 +35986,7 @@
       </c>
       <c r="F187" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -36305,10 +36003,10 @@
         <v>19</v>
       </c>
       <c r="J187" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K187" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L187" s="6" t="n">
         <v>27</v>
@@ -36320,7 +36018,7 @@
         <v>2</v>
       </c>
       <c r="O187" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P187" s="7" t="n">
         <v>27</v>
@@ -36334,10 +36032,8 @@
       <c r="S187" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T187" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T187" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U187" s="7" t="inlineStr">
         <is>
@@ -36486,7 +36182,7 @@
           <t>220820@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F188" s="9" t="inlineStr">
+      <c r="F188" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -36505,10 +36201,10 @@
         <v>20</v>
       </c>
       <c r="J188" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K188" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L188" s="6" t="n">
         <v>27</v>
@@ -36520,7 +36216,7 @@
         <v>1</v>
       </c>
       <c r="O188" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P188" s="7" t="n">
         <v>27</v>
@@ -36534,10 +36230,8 @@
       <c r="S188" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T188" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T188" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U188" s="7" t="inlineStr">
         <is>
@@ -36688,7 +36382,7 @@
       </c>
       <c r="F189" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -36705,10 +36399,10 @@
         <v>21</v>
       </c>
       <c r="J189" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K189" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L189" s="6" t="n">
         <v>27</v>
@@ -36720,7 +36414,7 @@
         <v>0</v>
       </c>
       <c r="O189" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P189" s="7" t="n">
         <v>27</v>
@@ -36734,10 +36428,8 @@
       <c r="S189" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T189" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T189" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U189" s="7" t="inlineStr">
         <is>
@@ -36888,7 +36580,7 @@
       </c>
       <c r="F190" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -36905,10 +36597,10 @@
         <v>21</v>
       </c>
       <c r="J190" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K190" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L190" s="6" t="n">
         <v>27</v>
@@ -36920,7 +36612,7 @@
         <v>0</v>
       </c>
       <c r="O190" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P190" s="7" t="n">
         <v>27</v>
@@ -36934,10 +36626,8 @@
       <c r="S190" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T190" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T190" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U190" s="7" t="inlineStr">
         <is>
@@ -37086,7 +36776,7 @@
           <t>220824@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F191" s="9" t="inlineStr">
+      <c r="F191" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -37105,10 +36795,10 @@
         <v>20</v>
       </c>
       <c r="J191" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K191" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L191" s="6" t="n">
         <v>27</v>
@@ -37120,7 +36810,7 @@
         <v>1</v>
       </c>
       <c r="O191" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P191" s="7" t="n">
         <v>27</v>
@@ -37134,10 +36824,8 @@
       <c r="S191" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T191" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T191" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U191" s="7" t="inlineStr">
         <is>
@@ -37288,7 +36976,7 @@
       </c>
       <c r="F192" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -37305,10 +36993,10 @@
         <v>19</v>
       </c>
       <c r="J192" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K192" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L192" s="6" t="n">
         <v>27</v>
@@ -37320,7 +37008,7 @@
         <v>2</v>
       </c>
       <c r="O192" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P192" s="7" t="n">
         <v>27</v>
@@ -37334,10 +37022,8 @@
       <c r="S192" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T192" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T192" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U192" s="7" t="inlineStr">
         <is>
@@ -37486,7 +37172,7 @@
           <t>220826@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F193" s="9" t="inlineStr">
+      <c r="F193" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -37505,10 +37191,10 @@
         <v>20</v>
       </c>
       <c r="J193" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K193" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L193" s="6" t="n">
         <v>27</v>
@@ -37520,7 +37206,7 @@
         <v>1</v>
       </c>
       <c r="O193" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P193" s="7" t="n">
         <v>27</v>
@@ -37534,10 +37220,8 @@
       <c r="S193" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T193" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T193" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U193" s="7" t="inlineStr">
         <is>
@@ -37688,7 +37372,7 @@
       </c>
       <c r="F194" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -37705,10 +37389,10 @@
         <v>19</v>
       </c>
       <c r="J194" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K194" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L194" s="6" t="n">
         <v>27</v>
@@ -37720,7 +37404,7 @@
         <v>2</v>
       </c>
       <c r="O194" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P194" s="7" t="n">
         <v>27</v>
@@ -37734,10 +37418,8 @@
       <c r="S194" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T194" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T194" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U194" s="7" t="inlineStr">
         <is>
@@ -37886,7 +37568,7 @@
           <t>220828@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F195" s="9" t="inlineStr">
+      <c r="F195" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -37905,10 +37587,10 @@
         <v>20</v>
       </c>
       <c r="J195" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K195" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L195" s="6" t="n">
         <v>27</v>
@@ -37920,7 +37602,7 @@
         <v>1</v>
       </c>
       <c r="O195" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P195" s="7" t="n">
         <v>27</v>
@@ -37934,10 +37616,8 @@
       <c r="S195" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T195" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T195" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U195" s="7" t="inlineStr">
         <is>
@@ -38088,7 +37768,7 @@
       </c>
       <c r="F196" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -38105,10 +37785,10 @@
         <v>19</v>
       </c>
       <c r="J196" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K196" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L196" s="6" t="n">
         <v>27</v>
@@ -38120,7 +37800,7 @@
         <v>2</v>
       </c>
       <c r="O196" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P196" s="7" t="n">
         <v>27</v>
@@ -38134,10 +37814,8 @@
       <c r="S196" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T196" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T196" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U196" s="7" t="inlineStr">
         <is>
@@ -38288,7 +37966,7 @@
       </c>
       <c r="F197" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -38305,10 +37983,10 @@
         <v>19</v>
       </c>
       <c r="J197" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K197" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L197" s="6" t="n">
         <v>27</v>
@@ -38320,7 +37998,7 @@
         <v>2</v>
       </c>
       <c r="O197" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P197" s="7" t="n">
         <v>27</v>
@@ -38334,10 +38012,8 @@
       <c r="S197" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T197" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T197" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U197" s="7" t="inlineStr">
         <is>
@@ -38486,7 +38162,7 @@
           <t>220832@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F198" s="9" t="inlineStr">
+      <c r="F198" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -38505,10 +38181,10 @@
         <v>20</v>
       </c>
       <c r="J198" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K198" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L198" s="6" t="n">
         <v>27</v>
@@ -38520,7 +38196,7 @@
         <v>1</v>
       </c>
       <c r="O198" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P198" s="7" t="n">
         <v>27</v>
@@ -38534,10 +38210,8 @@
       <c r="S198" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T198" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T198" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U198" s="7" t="inlineStr">
         <is>
@@ -38688,7 +38362,7 @@
       </c>
       <c r="F199" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -38705,10 +38379,10 @@
         <v>19</v>
       </c>
       <c r="J199" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K199" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L199" s="6" t="n">
         <v>27</v>
@@ -38720,7 +38394,7 @@
         <v>2</v>
       </c>
       <c r="O199" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P199" s="7" t="n">
         <v>27</v>
@@ -38734,10 +38408,8 @@
       <c r="S199" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T199" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T199" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U199" s="7" t="inlineStr">
         <is>
@@ -38886,7 +38558,7 @@
           <t>220834@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F200" s="9" t="inlineStr">
+      <c r="F200" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -38905,10 +38577,10 @@
         <v>20</v>
       </c>
       <c r="J200" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K200" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L200" s="6" t="n">
         <v>27</v>
@@ -38920,7 +38592,7 @@
         <v>1</v>
       </c>
       <c r="O200" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P200" s="7" t="n">
         <v>27</v>
@@ -38934,10 +38606,8 @@
       <c r="S200" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T200" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T200" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U200" s="7" t="inlineStr">
         <is>
@@ -39086,7 +38756,7 @@
           <t>220838@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F201" s="9" t="inlineStr">
+      <c r="F201" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -39105,10 +38775,10 @@
         <v>20</v>
       </c>
       <c r="J201" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K201" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L201" s="6" t="n">
         <v>27</v>
@@ -39120,7 +38790,7 @@
         <v>1</v>
       </c>
       <c r="O201" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P201" s="7" t="n">
         <v>27</v>
@@ -39134,10 +38804,8 @@
       <c r="S201" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T201" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T201" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U201" s="7" t="inlineStr">
         <is>
@@ -39288,7 +38956,7 @@
       </c>
       <c r="F202" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
@@ -39305,10 +38973,10 @@
         <v>21</v>
       </c>
       <c r="J202" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K202" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L202" s="6" t="n">
         <v>27</v>
@@ -39320,7 +38988,7 @@
         <v>0</v>
       </c>
       <c r="O202" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P202" s="7" t="n">
         <v>27</v>
@@ -39334,10 +39002,8 @@
       <c r="S202" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T202" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T202" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U202" s="7" t="inlineStr">
         <is>
@@ -39488,7 +39154,7 @@
       </c>
       <c r="F203" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -39505,10 +39171,10 @@
         <v>19</v>
       </c>
       <c r="J203" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K203" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L203" s="6" t="n">
         <v>27</v>
@@ -39520,7 +39186,7 @@
         <v>2</v>
       </c>
       <c r="O203" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P203" s="7" t="n">
         <v>27</v>
@@ -39534,10 +39200,8 @@
       <c r="S203" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T203" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T203" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U203" s="7" t="inlineStr">
         <is>
@@ -39688,7 +39352,7 @@
       </c>
       <c r="F204" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -39705,10 +39369,10 @@
         <v>21</v>
       </c>
       <c r="J204" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K204" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L204" s="6" t="n">
         <v>27</v>
@@ -39720,7 +39384,7 @@
         <v>0</v>
       </c>
       <c r="O204" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P204" s="7" t="n">
         <v>27</v>
@@ -39734,10 +39398,8 @@
       <c r="S204" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T204" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T204" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U204" s="7" t="inlineStr">
         <is>
@@ -39888,7 +39550,7 @@
       </c>
       <c r="F205" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -39905,10 +39567,10 @@
         <v>19</v>
       </c>
       <c r="J205" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K205" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L205" s="6" t="n">
         <v>27</v>
@@ -39920,7 +39582,7 @@
         <v>2</v>
       </c>
       <c r="O205" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P205" s="7" t="n">
         <v>27</v>
@@ -39934,10 +39596,8 @@
       <c r="S205" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T205" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T205" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U205" s="7" t="inlineStr">
         <is>
@@ -40088,7 +39748,7 @@
       </c>
       <c r="F206" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -40105,10 +39765,10 @@
         <v>19</v>
       </c>
       <c r="J206" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K206" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L206" s="6" t="n">
         <v>27</v>
@@ -40120,7 +39780,7 @@
         <v>2</v>
       </c>
       <c r="O206" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P206" s="7" t="n">
         <v>27</v>
@@ -40134,10 +39794,8 @@
       <c r="S206" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T206" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T206" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U206" s="7" t="inlineStr">
         <is>
@@ -40288,7 +39946,7 @@
       </c>
       <c r="F207" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -40305,10 +39963,10 @@
         <v>19</v>
       </c>
       <c r="J207" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K207" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L207" s="6" t="n">
         <v>27</v>
@@ -40320,7 +39978,7 @@
         <v>2</v>
       </c>
       <c r="O207" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P207" s="7" t="n">
         <v>27</v>
@@ -40334,10 +39992,8 @@
       <c r="S207" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T207" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T207" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U207" s="7" t="inlineStr">
         <is>
@@ -40488,7 +40144,7 @@
       </c>
       <c r="F208" s="9" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Moderate Risk</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -40505,10 +40161,10 @@
         <v>21</v>
       </c>
       <c r="J208" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K208" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L208" s="6" t="n">
         <v>27</v>
@@ -40520,7 +40176,7 @@
         <v>0</v>
       </c>
       <c r="O208" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P208" s="7" t="n">
         <v>27</v>
@@ -40534,10 +40190,8 @@
       <c r="S208" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T208" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T208" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U208" s="7" t="inlineStr">
         <is>
@@ -40688,7 +40342,7 @@
       </c>
       <c r="F209" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -40705,10 +40359,10 @@
         <v>19</v>
       </c>
       <c r="J209" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K209" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L209" s="6" t="n">
         <v>27</v>
@@ -40720,7 +40374,7 @@
         <v>2</v>
       </c>
       <c r="O209" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P209" s="7" t="n">
         <v>27</v>
@@ -40734,10 +40388,8 @@
       <c r="S209" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T209" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T209" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U209" s="7" t="inlineStr">
         <is>
@@ -40888,7 +40540,7 @@
       </c>
       <c r="F210" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -40905,10 +40557,10 @@
         <v>19</v>
       </c>
       <c r="J210" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K210" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L210" s="6" t="n">
         <v>27</v>
@@ -40920,7 +40572,7 @@
         <v>2</v>
       </c>
       <c r="O210" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P210" s="7" t="n">
         <v>27</v>
@@ -40934,10 +40586,8 @@
       <c r="S210" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T210" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T210" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U210" s="7" t="inlineStr">
         <is>
@@ -41086,7 +40736,7 @@
           <t>220879@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F211" s="9" t="inlineStr">
+      <c r="F211" s="8" t="inlineStr">
         <is>
           <t>Low Risk</t>
         </is>
@@ -41105,10 +40755,10 @@
         <v>20</v>
       </c>
       <c r="J211" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K211" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L211" s="6" t="n">
         <v>27</v>
@@ -41120,7 +40770,7 @@
         <v>1</v>
       </c>
       <c r="O211" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P211" s="7" t="n">
         <v>27</v>
@@ -41134,10 +40784,8 @@
       <c r="S211" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T211" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T211" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U211" s="7" t="inlineStr">
         <is>
@@ -41288,7 +40936,7 @@
       </c>
       <c r="F212" s="8" t="inlineStr">
         <is>
-          <t>No Risk</t>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -41305,10 +40953,10 @@
         <v>19</v>
       </c>
       <c r="J212" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K212" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L212" s="6" t="n">
         <v>27</v>
@@ -41320,7 +40968,7 @@
         <v>2</v>
       </c>
       <c r="O212" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P212" s="7" t="n">
         <v>27</v>
@@ -41334,10 +40982,8 @@
       <c r="S212" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T212" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T212" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="U212" s="7" t="inlineStr">
         <is>
@@ -41486,7 +41132,7 @@
           <t>220969@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F213" s="8" t="inlineStr">
+      <c r="F213" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -41690,7 +41336,7 @@
           <t>220970@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F214" s="8" t="inlineStr">
+      <c r="F214" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -41894,7 +41540,7 @@
           <t>220971@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F215" s="8" t="inlineStr">
+      <c r="F215" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -42098,7 +41744,7 @@
           <t>220972@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F216" s="8" t="inlineStr">
+      <c r="F216" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -42302,7 +41948,7 @@
           <t>220974@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F217" s="8" t="inlineStr">
+      <c r="F217" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -42506,7 +42152,7 @@
           <t>220979@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F218" s="8" t="inlineStr">
+      <c r="F218" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -42710,7 +42356,7 @@
           <t>220983@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F219" s="8" t="inlineStr">
+      <c r="F219" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -42914,7 +42560,7 @@
           <t>220986@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F220" s="8" t="inlineStr">
+      <c r="F220" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -43118,7 +42764,7 @@
           <t>220989@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F221" s="8" t="inlineStr">
+      <c r="F221" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -43322,7 +42968,7 @@
           <t>220991@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F222" s="8" t="inlineStr">
+      <c r="F222" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -43526,7 +43172,7 @@
           <t>220992@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F223" s="8" t="inlineStr">
+      <c r="F223" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -43730,7 +43376,7 @@
           <t>220996@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F224" s="8" t="inlineStr">
+      <c r="F224" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -43934,7 +43580,7 @@
           <t>220997@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F225" s="8" t="inlineStr">
+      <c r="F225" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -44138,7 +43784,7 @@
           <t>221002@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F226" s="8" t="inlineStr">
+      <c r="F226" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -44342,7 +43988,7 @@
           <t>221006@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F227" s="8" t="inlineStr">
+      <c r="F227" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -44546,7 +44192,7 @@
           <t>221008@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F228" s="8" t="inlineStr">
+      <c r="F228" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -44750,7 +44396,7 @@
           <t>221012@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F229" s="8" t="inlineStr">
+      <c r="F229" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -44954,7 +44600,7 @@
           <t>221015@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F230" s="8" t="inlineStr">
+      <c r="F230" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -45158,7 +44804,7 @@
           <t>221016@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F231" s="8" t="inlineStr">
+      <c r="F231" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -45362,7 +45008,7 @@
           <t>221018@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F232" s="8" t="inlineStr">
+      <c r="F232" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -45566,7 +45212,7 @@
           <t>221020@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F233" s="8" t="inlineStr">
+      <c r="F233" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -45770,7 +45416,7 @@
           <t>221021@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F234" s="8" t="inlineStr">
+      <c r="F234" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -45974,7 +45620,7 @@
           <t>221023@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F235" s="8" t="inlineStr">
+      <c r="F235" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -46178,7 +45824,7 @@
           <t>221025@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F236" s="8" t="inlineStr">
+      <c r="F236" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -46382,7 +46028,7 @@
           <t>221029@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F237" s="8" t="inlineStr">
+      <c r="F237" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -46586,7 +46232,7 @@
           <t>221035@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F238" s="8" t="inlineStr">
+      <c r="F238" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -46790,7 +46436,7 @@
           <t>221036@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F239" s="8" t="inlineStr">
+      <c r="F239" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -46994,7 +46640,7 @@
           <t>221037@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F240" s="8" t="inlineStr">
+      <c r="F240" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -47198,7 +46844,7 @@
           <t>221040@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F241" s="8" t="inlineStr">
+      <c r="F241" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -47402,7 +47048,7 @@
           <t>221046@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F242" s="8" t="inlineStr">
+      <c r="F242" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -47606,7 +47252,7 @@
           <t>221047@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F243" s="8" t="inlineStr">
+      <c r="F243" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -47810,7 +47456,7 @@
           <t>221048@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F244" s="8" t="inlineStr">
+      <c r="F244" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -48014,7 +47660,7 @@
           <t>221049@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F245" s="8" t="inlineStr">
+      <c r="F245" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -48218,7 +47864,7 @@
           <t>221050@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F246" s="8" t="inlineStr">
+      <c r="F246" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -48422,7 +48068,7 @@
           <t>221051@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F247" s="8" t="inlineStr">
+      <c r="F247" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -48626,7 +48272,7 @@
           <t>221052@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F248" s="8" t="inlineStr">
+      <c r="F248" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -48830,7 +48476,7 @@
           <t>221053@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F249" s="8" t="inlineStr">
+      <c r="F249" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -49034,7 +48680,7 @@
           <t>221054@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F250" s="8" t="inlineStr">
+      <c r="F250" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -49238,7 +48884,7 @@
           <t>221055@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F251" s="8" t="inlineStr">
+      <c r="F251" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -49442,7 +49088,7 @@
           <t>221056@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F252" s="8" t="inlineStr">
+      <c r="F252" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -49646,7 +49292,7 @@
           <t>221059@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F253" s="8" t="inlineStr">
+      <c r="F253" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -49850,7 +49496,7 @@
           <t>221060@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F254" s="8" t="inlineStr">
+      <c r="F254" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -50054,7 +49700,7 @@
           <t>221062@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F255" s="8" t="inlineStr">
+      <c r="F255" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -50258,7 +49904,7 @@
           <t>221063@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F256" s="8" t="inlineStr">
+      <c r="F256" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -50462,7 +50108,7 @@
           <t>221064@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F257" s="8" t="inlineStr">
+      <c r="F257" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -50666,7 +50312,7 @@
           <t>221066@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F258" s="8" t="inlineStr">
+      <c r="F258" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -50870,7 +50516,7 @@
           <t>221067@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F259" s="8" t="inlineStr">
+      <c r="F259" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -51074,7 +50720,7 @@
           <t>221068@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F260" s="8" t="inlineStr">
+      <c r="F260" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -51278,7 +50924,7 @@
           <t>221069@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F261" s="8" t="inlineStr">
+      <c r="F261" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -51482,7 +51128,7 @@
           <t>221070@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F262" s="8" t="inlineStr">
+      <c r="F262" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -51686,7 +51332,7 @@
           <t>221071@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F263" s="8" t="inlineStr">
+      <c r="F263" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -51890,7 +51536,7 @@
           <t>221072@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F264" s="8" t="inlineStr">
+      <c r="F264" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -52094,7 +51740,7 @@
           <t>221073@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F265" s="8" t="inlineStr">
+      <c r="F265" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -52298,7 +51944,7 @@
           <t>221075@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F266" s="8" t="inlineStr">
+      <c r="F266" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -52502,7 +52148,7 @@
           <t>221076@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F267" s="8" t="inlineStr">
+      <c r="F267" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -52706,7 +52352,7 @@
           <t>221077@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F268" s="8" t="inlineStr">
+      <c r="F268" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -52910,7 +52556,7 @@
           <t>221078@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F269" s="8" t="inlineStr">
+      <c r="F269" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -53114,7 +52760,7 @@
           <t>221079@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F270" s="8" t="inlineStr">
+      <c r="F270" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -53318,7 +52964,7 @@
           <t>221080@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F271" s="8" t="inlineStr">
+      <c r="F271" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -53522,7 +53168,7 @@
           <t>221084@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F272" s="8" t="inlineStr">
+      <c r="F272" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -53726,7 +53372,7 @@
           <t>221085@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F273" s="8" t="inlineStr">
+      <c r="F273" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -53930,7 +53576,7 @@
           <t>221086@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F274" s="8" t="inlineStr">
+      <c r="F274" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -54134,7 +53780,7 @@
           <t>221087@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F275" s="8" t="inlineStr">
+      <c r="F275" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -54338,7 +53984,7 @@
           <t>221088@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F276" s="8" t="inlineStr">
+      <c r="F276" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -54542,7 +54188,7 @@
           <t>221089@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F277" s="8" t="inlineStr">
+      <c r="F277" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -54746,7 +54392,7 @@
           <t>221090@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F278" s="8" t="inlineStr">
+      <c r="F278" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -54950,7 +54596,7 @@
           <t>221091@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F279" s="8" t="inlineStr">
+      <c r="F279" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -55154,7 +54800,7 @@
           <t>221092@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F280" s="8" t="inlineStr">
+      <c r="F280" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -55358,7 +55004,7 @@
           <t>221093@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F281" s="8" t="inlineStr">
+      <c r="F281" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -55562,7 +55208,7 @@
           <t>221095@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F282" s="8" t="inlineStr">
+      <c r="F282" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -55766,7 +55412,7 @@
           <t>221096@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F283" s="8" t="inlineStr">
+      <c r="F283" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -55970,7 +55616,7 @@
           <t>221097@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F284" s="8" t="inlineStr">
+      <c r="F284" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -56174,7 +55820,7 @@
           <t>221099@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F285" s="8" t="inlineStr">
+      <c r="F285" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -56378,7 +56024,7 @@
           <t>221100@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F286" s="8" t="inlineStr">
+      <c r="F286" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -56582,7 +56228,7 @@
           <t>221101@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F287" s="8" t="inlineStr">
+      <c r="F287" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -56786,7 +56432,7 @@
           <t>221102@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F288" s="8" t="inlineStr">
+      <c r="F288" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -56990,7 +56636,7 @@
           <t>221103@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F289" s="8" t="inlineStr">
+      <c r="F289" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -57194,7 +56840,7 @@
           <t>221104@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F290" s="8" t="inlineStr">
+      <c r="F290" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -57398,7 +57044,7 @@
           <t>221106@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F291" s="8" t="inlineStr">
+      <c r="F291" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -57602,7 +57248,7 @@
           <t>221108@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F292" s="8" t="inlineStr">
+      <c r="F292" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -57806,7 +57452,7 @@
           <t>221110@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F293" s="8" t="inlineStr">
+      <c r="F293" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -58010,7 +57656,7 @@
           <t>221111@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F294" s="8" t="inlineStr">
+      <c r="F294" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -58214,7 +57860,7 @@
           <t>221112@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F295" s="8" t="inlineStr">
+      <c r="F295" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -58418,7 +58064,7 @@
           <t>221114@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F296" s="8" t="inlineStr">
+      <c r="F296" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -58622,7 +58268,7 @@
           <t>221116@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F297" s="8" t="inlineStr">
+      <c r="F297" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -58826,7 +58472,7 @@
           <t>221117@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F298" s="8" t="inlineStr">
+      <c r="F298" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -59030,7 +58676,7 @@
           <t>221118@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F299" s="8" t="inlineStr">
+      <c r="F299" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -59234,7 +58880,7 @@
           <t>221119@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F300" s="8" t="inlineStr">
+      <c r="F300" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -59438,7 +59084,7 @@
           <t>221120@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F301" s="8" t="inlineStr">
+      <c r="F301" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -59642,7 +59288,7 @@
           <t>221121@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F302" s="8" t="inlineStr">
+      <c r="F302" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -59846,7 +59492,7 @@
           <t>221122@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F303" s="8" t="inlineStr">
+      <c r="F303" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -60050,7 +59696,7 @@
           <t>221123@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F304" s="8" t="inlineStr">
+      <c r="F304" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -60254,7 +59900,7 @@
           <t>221124@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F305" s="8" t="inlineStr">
+      <c r="F305" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -60458,7 +60104,7 @@
           <t>221125@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F306" s="8" t="inlineStr">
+      <c r="F306" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -60662,7 +60308,7 @@
           <t>221126@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F307" s="8" t="inlineStr">
+      <c r="F307" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -60866,7 +60512,7 @@
           <t>221127@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F308" s="8" t="inlineStr">
+      <c r="F308" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -61070,7 +60716,7 @@
           <t>221128@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F309" s="8" t="inlineStr">
+      <c r="F309" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -61274,7 +60920,7 @@
           <t>221129@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F310" s="8" t="inlineStr">
+      <c r="F310" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -61478,7 +61124,7 @@
           <t>221130@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F311" s="8" t="inlineStr">
+      <c r="F311" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -61682,7 +61328,7 @@
           <t>221131@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F312" s="8" t="inlineStr">
+      <c r="F312" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -61886,7 +61532,7 @@
           <t>221132@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F313" s="8" t="inlineStr">
+      <c r="F313" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -62090,7 +61736,7 @@
           <t>221133@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F314" s="8" t="inlineStr">
+      <c r="F314" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -62294,7 +61940,7 @@
           <t>221134@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F315" s="8" t="inlineStr">
+      <c r="F315" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -62498,7 +62144,7 @@
           <t>221136@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F316" s="8" t="inlineStr">
+      <c r="F316" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -62702,7 +62348,7 @@
           <t>221137@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F317" s="8" t="inlineStr">
+      <c r="F317" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -62906,7 +62552,7 @@
           <t>221138@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F318" s="8" t="inlineStr">
+      <c r="F318" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -63110,7 +62756,7 @@
           <t>221139@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F319" s="8" t="inlineStr">
+      <c r="F319" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -63314,7 +62960,7 @@
           <t>221140@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F320" s="8" t="inlineStr">
+      <c r="F320" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -63518,7 +63164,7 @@
           <t>221141@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F321" s="8" t="inlineStr">
+      <c r="F321" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -63722,7 +63368,7 @@
           <t>221144@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F322" s="8" t="inlineStr">
+      <c r="F322" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -63926,7 +63572,7 @@
           <t>221145@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F323" s="8" t="inlineStr">
+      <c r="F323" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -64130,7 +63776,7 @@
           <t>221146@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F324" s="8" t="inlineStr">
+      <c r="F324" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -64334,7 +63980,7 @@
           <t>221147@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F325" s="8" t="inlineStr">
+      <c r="F325" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -64538,7 +64184,7 @@
           <t>221148@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F326" s="8" t="inlineStr">
+      <c r="F326" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -64742,7 +64388,7 @@
           <t>221149@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F327" s="8" t="inlineStr">
+      <c r="F327" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -64946,7 +64592,7 @@
           <t>221150@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F328" s="8" t="inlineStr">
+      <c r="F328" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -65150,7 +64796,7 @@
           <t>221151@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F329" s="8" t="inlineStr">
+      <c r="F329" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -65354,7 +65000,7 @@
           <t>221152@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F330" s="8" t="inlineStr">
+      <c r="F330" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -65558,7 +65204,7 @@
           <t>221153@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F331" s="8" t="inlineStr">
+      <c r="F331" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -65762,7 +65408,7 @@
           <t>221154@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F332" s="8" t="inlineStr">
+      <c r="F332" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -65966,7 +65612,7 @@
           <t>221157@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F333" s="8" t="inlineStr">
+      <c r="F333" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -66170,7 +65816,7 @@
           <t>221158@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F334" s="8" t="inlineStr">
+      <c r="F334" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -66374,7 +66020,7 @@
           <t>221159@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F335" s="8" t="inlineStr">
+      <c r="F335" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -66578,7 +66224,7 @@
           <t>221160@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F336" s="8" t="inlineStr">
+      <c r="F336" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -66782,7 +66428,7 @@
           <t>221161@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F337" s="8" t="inlineStr">
+      <c r="F337" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -66986,7 +66632,7 @@
           <t>221162@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F338" s="8" t="inlineStr">
+      <c r="F338" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -67190,7 +66836,7 @@
           <t>221163@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F339" s="8" t="inlineStr">
+      <c r="F339" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -67394,7 +67040,7 @@
           <t>221164@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F340" s="8" t="inlineStr">
+      <c r="F340" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -67598,7 +67244,7 @@
           <t>221165@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F341" s="8" t="inlineStr">
+      <c r="F341" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -67802,7 +67448,7 @@
           <t>221166@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F342" s="8" t="inlineStr">
+      <c r="F342" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -68006,7 +67652,7 @@
           <t>221167@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F343" s="8" t="inlineStr">
+      <c r="F343" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -68210,7 +67856,7 @@
           <t>221168@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F344" s="8" t="inlineStr">
+      <c r="F344" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -68414,7 +68060,7 @@
           <t>221169@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F345" s="8" t="inlineStr">
+      <c r="F345" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -68618,7 +68264,7 @@
           <t>221170@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F346" s="8" t="inlineStr">
+      <c r="F346" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -68822,7 +68468,7 @@
           <t>221174@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F347" s="8" t="inlineStr">
+      <c r="F347" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -69026,7 +68672,7 @@
           <t>221179@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F348" s="8" t="inlineStr">
+      <c r="F348" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -69230,7 +68876,7 @@
           <t>221181@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F349" s="8" t="inlineStr">
+      <c r="F349" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -69434,7 +69080,7 @@
           <t>221202@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F350" s="8" t="inlineStr">
+      <c r="F350" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -69638,7 +69284,7 @@
           <t>221206@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F351" s="8" t="inlineStr">
+      <c r="F351" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -69842,7 +69488,7 @@
           <t>221211@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F352" s="8" t="inlineStr">
+      <c r="F352" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -70046,7 +69692,7 @@
           <t>221214@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F353" s="8" t="inlineStr">
+      <c r="F353" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -70250,7 +69896,7 @@
           <t>221217@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F354" s="8" t="inlineStr">
+      <c r="F354" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -70454,7 +70100,7 @@
           <t>221224@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F355" s="8" t="inlineStr">
+      <c r="F355" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -70658,7 +70304,7 @@
           <t>221228@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F356" s="8" t="inlineStr">
+      <c r="F356" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -70862,7 +70508,7 @@
           <t>221234@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F357" s="8" t="inlineStr">
+      <c r="F357" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -71066,7 +70712,7 @@
           <t>221237@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F358" s="8" t="inlineStr">
+      <c r="F358" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -71270,7 +70916,7 @@
           <t>221335@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F359" s="8" t="inlineStr">
+      <c r="F359" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -71474,7 +71120,7 @@
           <t>221541@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F360" s="8" t="inlineStr">
+      <c r="F360" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -71678,7 +71324,7 @@
           <t>221625@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F361" s="8" t="inlineStr">
+      <c r="F361" s="10" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
@@ -71885,57 +71531,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Student ID</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Validation Group</t>
         </is>
@@ -85418,37 +85064,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Student ID</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Group Before</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Group After</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Transfer Date</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
